--- a/گزارش_جامع_اعتباری_مشتریان_صیادی_۱۴۰۵۰۶۱۵.xlsx
+++ b/گزارش_جامع_اعتباری_مشتریان_صیادی_۱۴۰۵۰۶۱۵.xlsx
@@ -130,7 +130,7 @@
       <name val="Tahoma"/>
       <b val="1"/>
       <color rgb="001E3A8A"/>
-      <sz val="9"/>
+      <sz val="8.5"/>
     </font>
     <font>
       <name val="Tahoma"/>
@@ -292,7 +292,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -355,13 +355,10 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -373,13 +370,10 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -391,13 +385,10 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -409,13 +400,10 @@
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -424,16 +412,28 @@
     <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -454,13 +454,23 @@
     <xf numFmtId="2" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -470,22 +480,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -518,14 +512,11 @@
     <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -574,13 +565,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -963,16 +966,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="58" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="64" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="65" customWidth="1" min="10" max="10"/>
@@ -988,7 +991,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>سامانه هوشمند مدیریت اعتباری صیاد | تاریخ گزارش: 1405/06/16 ساعت 07:59:47 | مبنای محاسبات: تجمیع تک‌باره صادرکننده یکتا و حذف قطعی خطای دوباره‌شماری</t>
+          <t>سامانه هوشمند مدیریت اعتباری صیاد | تاریخ مبنای استعلام: 1405/06/15 | زمان تولید گزارش: 1405/06/16 ساعت 08:29:11 | مبنای محاسبات: تجمیع تک‌باره صادرکننده یکتا و حذف قطعی خطای دوباره‌شماری</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1239,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>۲۳۶.۴۱۵ میلیارد ریال از ۲۴۴.۷۵۱ میلیارد ریال برگشتی</t>
+          <t>۲۳۶.۴۲۵ میلیارد ریال از ۲۴۴.۷۵۱ میلیارد ریال برگشتی</t>
         </is>
       </c>
     </row>
@@ -1246,8 +1249,9 @@
           <t>تعداد صادرکنندگان دارای چک برگشتی فعال</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n">
-        <v>10</v>
+      <c r="B17" s="10">
+        <f>COUNTIF('02_مشتریان_یکتا'!K4:K49, "&gt;0")</f>
+        <v/>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
@@ -1256,7 +1260,7 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>۱۰ صادرکننده با برگشتی مثبت در میان پروفایل‌های معتبر</t>
+          <t>۱۳ صادرکننده با برگشتی مثبت در میان ۴۶ پروفایل معتبر بانکی</t>
         </is>
       </c>
     </row>
@@ -1329,591 +1333,667 @@
           <t>۸۱ تا ۱۰۰</t>
         </is>
       </c>
-      <c r="C24" s="22" t="n">
+      <c r="C24" s="22">
+        <f>COUNTIF('02_مشتریان_یکتا'!$R$4:$R$49, "اقدام فوری")</f>
+        <v/>
+      </c>
+      <c r="D24" s="23">
+        <f>C24/$B$6</f>
+        <v/>
+      </c>
+      <c r="E24" s="22">
+        <f>SUMIFS('02_مشتریان_یکتا'!$H$4:$H$49, '02_مشتریان_یکتا'!$R$4:$R$49, "اقدام فوری")</f>
+        <v/>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>توقف فوری افزایش اعتبار، ضبط وثایق و پیگیری حقوقی وصول</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>پرریسک (High Risk)</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>۶۱ تا ۸۰</t>
+        </is>
+      </c>
+      <c r="C25" s="27">
+        <f>COUNTIF('02_مشتریان_یکتا'!$R$4:$R$49, "پرریسک")</f>
+        <v/>
+      </c>
+      <c r="D25" s="28">
+        <f>C25/$B$6</f>
+        <v/>
+      </c>
+      <c r="E25" s="27">
+        <f>SUMIFS('02_مشتریان_یکتا'!$H$4:$H$49, '02_مشتریان_یکتا'!$R$4:$R$49, "پرریسک")</f>
+        <v/>
+      </c>
+      <c r="F25" s="29" t="inlineStr">
+        <is>
+          <t>درخواست وثیقه ملکی/نقد، کاهش سقف و کنترل مستمر</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>مراقبت (Watch List)</t>
+        </is>
+      </c>
+      <c r="B26" s="31" t="inlineStr">
+        <is>
+          <t>۴۱ تا ۶۰</t>
+        </is>
+      </c>
+      <c r="C26" s="32">
+        <f>COUNTIF('02_مشتریان_یکتا'!$R$4:$R$49, "مراقبت")</f>
+        <v/>
+      </c>
+      <c r="D26" s="33">
+        <f>C26/$B$6</f>
+        <v/>
+      </c>
+      <c r="E26" s="32">
+        <f>SUMIFS('02_مشتریان_یکتا'!$H$4:$H$49, '02_مشتریان_یکتا'!$R$4:$R$49, "مراقبت")</f>
+        <v/>
+      </c>
+      <c r="F26" s="34" t="inlineStr">
+        <is>
+          <t>اخذ تضمین فرعی، تبدیل چک مدت‌دار به نقد، پایش هفتگی و روزانه</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="35" t="inlineStr">
+        <is>
+          <t>عادی (Normal)</t>
+        </is>
+      </c>
+      <c r="B27" s="36" t="inlineStr">
+        <is>
+          <t>۲۱ تا ۴۰</t>
+        </is>
+      </c>
+      <c r="C27" s="37">
+        <f>COUNTIF('02_مشتریان_یکتا'!$R$4:$R$49, "عادی")</f>
+        <v/>
+      </c>
+      <c r="D27" s="38">
+        <f>C27/$B$6</f>
+        <v/>
+      </c>
+      <c r="E27" s="37">
+        <f>SUMIFS('02_مشتریان_یکتا'!$H$4:$H$49, '02_مشتریان_یکتا'!$R$4:$R$49, "عادی")</f>
+        <v/>
+      </c>
+      <c r="F27" s="35" t="inlineStr">
+        <is>
+          <t>روال استاندارد اعتباری و پایش سررسیدها</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="39" t="inlineStr">
+        <is>
+          <t>کم‌ریسک (Low Risk)</t>
+        </is>
+      </c>
+      <c r="B28" s="40" t="inlineStr">
+        <is>
+          <t>۰ تا ۲۰</t>
+        </is>
+      </c>
+      <c r="C28" s="41">
+        <f>COUNTIF('02_مشتریان_یکتا'!$R$4:$R$49, "کم‌ریسک")</f>
+        <v/>
+      </c>
+      <c r="D28" s="42">
+        <f>C28/$B$6</f>
+        <v/>
+      </c>
+      <c r="E28" s="41">
+        <f>SUMIFS('02_مشتریان_یکتا'!$H$4:$H$49, '02_مشتریان_یکتا'!$R$4:$R$49, "کم‌ریسک")</f>
+        <v/>
+      </c>
+      <c r="F28" s="43" t="inlineStr">
+        <is>
+          <t>پذیرش چک و اعطای سقف حداکثری تسهیلات تجاری</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="44" t="inlineStr">
+        <is>
+          <t>مجموع کل طبقات اعتباری</t>
+        </is>
+      </c>
+      <c r="B29" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C29" s="46">
+        <f>SUM(C24:C28)</f>
+        <v/>
+      </c>
+      <c r="D29" s="47">
+        <f>SUM(D24:D28)</f>
+        <v/>
+      </c>
+      <c r="E29" s="46">
+        <f>SUM(E24:E28)</f>
+        <v/>
+      </c>
+      <c r="F29" s="48" t="inlineStr">
+        <is>
+          <t>تطابق ۱۰۰٪ با ۴۶ پروفایل معتبر و ۴۷۹.۷۰۵ میلیارد ریال صندوق</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>۱۰ صادرکننده پرریسک صدر جدول و شاخص تمرکز هرفیندال (Top 10 High-Risk Issuers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>رتبه</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>نام صادرکننده</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>کدملی صادرکننده</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>مبلغ برگشتی بانکی (ریال)</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>سهم از کل برگشتی</t>
+        </is>
+      </c>
+      <c r="F32" s="19" t="inlineStr">
+        <is>
+          <t>سهم تجمعی (٪)</t>
+        </is>
+      </c>
+      <c r="G32" s="19" t="inlineStr">
+        <is>
+          <t>سهم در HHI</t>
+        </is>
+      </c>
+      <c r="H32" s="19" t="inlineStr">
+        <is>
+          <t>امتیاز ریسک</t>
+        </is>
+      </c>
+      <c r="I32" s="19" t="inlineStr">
+        <is>
+          <t>رده ریسک</t>
+        </is>
+      </c>
+      <c r="J32" s="19" t="inlineStr">
+        <is>
+          <t>تصمیم اعتباری سامانه</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="23" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="E24" s="24" t="n">
-        <v>1060000000</v>
-      </c>
-      <c r="F24" s="25" t="inlineStr">
-        <is>
-          <t>توقف فوری افزایش اعتبار، ضبط وثایق و پیگیری حقوقی وصول</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="26" t="inlineStr">
-        <is>
-          <t>پرریسک (High Risk)</t>
-        </is>
-      </c>
-      <c r="B25" s="27" t="inlineStr">
-        <is>
-          <t>۶۱ تا ۸۰</t>
-        </is>
-      </c>
-      <c r="C25" s="28" t="n">
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>حسین حشمتی</t>
+        </is>
+      </c>
+      <c r="C33" s="49" t="inlineStr">
+        <is>
+          <t>0933387075</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>56960000000</v>
+      </c>
+      <c r="E33" s="50" t="n">
+        <v>0.232726321853639</v>
+      </c>
+      <c r="F33" s="50" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="G33" s="51" t="n">
+        <v>541.62</v>
+      </c>
+      <c r="H33" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>اقدام فوری</t>
+        </is>
+      </c>
+      <c r="J33" s="12" t="inlineStr">
+        <is>
+          <t>مسدودسازی کامل تسهیلات، مطالبه وثیقه ملکی/نقدی، اقدام حقوقی و وصول آنی.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>وحید زوار</t>
+        </is>
+      </c>
+      <c r="C34" s="52" t="inlineStr">
+        <is>
+          <t>6430003159</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="n">
+        <v>46080000000</v>
+      </c>
+      <c r="E34" s="53" t="n">
+        <v>0.1882729794771012</v>
+      </c>
+      <c r="F34" s="53" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="G34" s="54" t="n">
+        <v>354.47</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>پرریسک</t>
+        </is>
+      </c>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>مسدودسازی سقف تسهیلات، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>محمد رفیق طرقی</t>
+        </is>
+      </c>
+      <c r="C35" s="49" t="inlineStr">
+        <is>
+          <t>0890543331</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>40300000000</v>
+      </c>
+      <c r="E35" s="50" t="n">
+        <v>0.1646571413395655</v>
+      </c>
+      <c r="F35" s="50" t="n">
+        <v>0.5857</v>
+      </c>
+      <c r="G35" s="51" t="n">
+        <v>271.12</v>
+      </c>
+      <c r="H35" s="10" t="n">
+        <v>78</v>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>پرریسک</t>
+        </is>
+      </c>
+      <c r="J35" s="12" t="inlineStr">
+        <is>
+          <t>مسدودسازی سقف تسهیلات، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>محمدجواد وفادار عیدگاهی</t>
+        </is>
+      </c>
+      <c r="C36" s="52" t="inlineStr">
+        <is>
+          <t>0924020865</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="n">
+        <v>21630000000</v>
+      </c>
+      <c r="E36" s="53" t="n">
+        <v>0.08837553268423827</v>
+      </c>
+      <c r="F36" s="53" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="G36" s="54" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>پرریسک</t>
+        </is>
+      </c>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>مسدودسازی سقف تسهیلات، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>محمد ضیافتی مالدار</t>
+        </is>
+      </c>
+      <c r="C37" s="49" t="inlineStr">
+        <is>
+          <t>0922236992</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>19160000000</v>
+      </c>
+      <c r="E37" s="50" t="n">
+        <v>0.07828364337632941</v>
+      </c>
+      <c r="F37" s="50" t="n">
+        <v>0.7523000000000001</v>
+      </c>
+      <c r="G37" s="51" t="n">
+        <v>61.28</v>
+      </c>
+      <c r="H37" s="10" t="n">
+        <v>72</v>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>پرریسک</t>
+        </is>
+      </c>
+      <c r="J37" s="12" t="inlineStr">
+        <is>
+          <t>مسدودسازی سقف تسهیلات، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>ابوالفضل شافعی</t>
+        </is>
+      </c>
+      <c r="C38" s="52" t="inlineStr">
+        <is>
+          <t>0941987231</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="n">
+        <v>12800000000</v>
+      </c>
+      <c r="E38" s="53" t="n">
+        <v>0.05229804985475034</v>
+      </c>
+      <c r="F38" s="53" t="n">
+        <v>0.8046</v>
+      </c>
+      <c r="G38" s="54" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>پرریسک</t>
+        </is>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>مسدودسازی سقف تسهیلات، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>زهرا بهرامی پویا</t>
+        </is>
+      </c>
+      <c r="C39" s="49" t="inlineStr">
+        <is>
+          <t>0927624011</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>12300000000</v>
+      </c>
+      <c r="E39" s="50" t="n">
+        <v>0.05025515728229915</v>
+      </c>
+      <c r="F39" s="50" t="n">
+        <v>0.8549</v>
+      </c>
+      <c r="G39" s="51" t="n">
+        <v>25.26</v>
+      </c>
+      <c r="H39" s="10" t="n">
+        <v>72</v>
+      </c>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>پرریسک</t>
+        </is>
+      </c>
+      <c r="J39" s="12" t="inlineStr">
+        <is>
+          <t>مسدودسازی سقف تسهیلات، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>احمد زحمتکش باجگیران</t>
+        </is>
+      </c>
+      <c r="C40" s="52" t="inlineStr">
+        <is>
+          <t>0860270361</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="n">
+        <v>11550000000</v>
+      </c>
+      <c r="E40" s="53" t="n">
+        <v>0.04719081842362238</v>
+      </c>
+      <c r="F40" s="53" t="n">
+        <v>0.9020999999999999</v>
+      </c>
+      <c r="G40" s="54" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>پرریسک</t>
+        </is>
+      </c>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>مسدودسازی سقف تسهیلات، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="D25" s="29" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="E25" s="30" t="n">
-        <v>125845000000</v>
-      </c>
-      <c r="F25" s="31" t="inlineStr">
-        <is>
-          <t>درخواست وثیقه ملکی/نقد، کاهش سقف و کنترل مستمر</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="32" t="inlineStr">
-        <is>
-          <t>مراقبت (Watch List)</t>
-        </is>
-      </c>
-      <c r="B26" s="33" t="inlineStr">
-        <is>
-          <t>۴۱ تا ۶۰</t>
-        </is>
-      </c>
-      <c r="C26" s="34" t="n">
-        <v>4</v>
-      </c>
-      <c r="D26" s="35" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="E26" s="36" t="n">
-        <v>38650000000</v>
-      </c>
-      <c r="F26" s="37" t="inlineStr">
-        <is>
-          <t>اخذ تضمین فرعی، تبدیل چک مدت‌دار به نقد، پایش هفتگی</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="38" t="inlineStr">
-        <is>
-          <t>عادی (Normal)</t>
-        </is>
-      </c>
-      <c r="B27" s="39" t="inlineStr">
-        <is>
-          <t>۲۱ تا ۴۰</t>
-        </is>
-      </c>
-      <c r="C27" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="38" t="inlineStr">
-        <is>
-          <t>روال استاندارد اعتباری و پایش سررسیدها</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="43" t="inlineStr">
-        <is>
-          <t>کم‌ریسک (Low Risk)</t>
-        </is>
-      </c>
-      <c r="B28" s="44" t="inlineStr">
-        <is>
-          <t>۰ تا ۲۰</t>
-        </is>
-      </c>
-      <c r="C28" s="45" t="n">
-        <v>32</v>
-      </c>
-      <c r="D28" s="46" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="E28" s="47" t="n">
-        <v>314150000000</v>
-      </c>
-      <c r="F28" s="48" t="inlineStr">
-        <is>
-          <t>پذیرش چک و اعطای سقف حداکثری تسهیلات تجاری</t>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>۱۰ صادرکننده پرریسک صدر جدول و شاخص تمرکز هرفیندال (Top 10 High-Risk Issuers)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>رتبه</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="inlineStr">
-        <is>
-          <t>نام صادرکننده</t>
-        </is>
-      </c>
-      <c r="C31" s="19" t="inlineStr">
-        <is>
-          <t>کدملی صادرکننده</t>
-        </is>
-      </c>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>مبلغ برگشتی بانکی (ریال)</t>
-        </is>
-      </c>
-      <c r="E31" s="19" t="inlineStr">
-        <is>
-          <t>سهم از کل برگشتی</t>
-        </is>
-      </c>
-      <c r="F31" s="19" t="inlineStr">
-        <is>
-          <t>سهم تجمعی (٪)</t>
-        </is>
-      </c>
-      <c r="G31" s="19" t="inlineStr">
-        <is>
-          <t>سهم در HHI</t>
-        </is>
-      </c>
-      <c r="H31" s="19" t="inlineStr">
-        <is>
-          <t>امتیاز ریسک</t>
-        </is>
-      </c>
-      <c r="I31" s="19" t="inlineStr">
-        <is>
-          <t>رده ریسک</t>
-        </is>
-      </c>
-      <c r="J31" s="19" t="inlineStr">
-        <is>
-          <t>تصمیم اعتباری سامانه</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B32" s="12" t="inlineStr">
-        <is>
-          <t>حسین حشمتی</t>
-        </is>
-      </c>
-      <c r="C32" s="49" t="inlineStr">
-        <is>
-          <t>0933387075</t>
-        </is>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>56960000000</v>
-      </c>
-      <c r="E32" s="50" t="n">
-        <v>0.232726321853639</v>
-      </c>
-      <c r="F32" s="50" t="n">
-        <v>0.2327</v>
-      </c>
-      <c r="G32" s="51" t="n">
-        <v>541.62</v>
-      </c>
-      <c r="H32" s="10" t="n">
-        <v>85</v>
-      </c>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t>اقدام فوری</t>
-        </is>
-      </c>
-      <c r="J32" s="12" t="inlineStr">
-        <is>
-          <t>توقف فوری تخصیص اعتبار، مطالبه وثیقه ملکی/نقدی، اقدام حقوقی و وصول آنی.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>وحید زوار</t>
-        </is>
-      </c>
-      <c r="C33" s="52" t="inlineStr">
-        <is>
-          <t>6430003159</t>
-        </is>
-      </c>
-      <c r="D33" s="13" t="n">
-        <v>46080000000</v>
-      </c>
-      <c r="E33" s="53" t="n">
-        <v>0.1882729794771012</v>
-      </c>
-      <c r="F33" s="53" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="G33" s="54" t="n">
-        <v>354.47</v>
-      </c>
-      <c r="H33" s="6" t="n">
-        <v>78</v>
-      </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>محمد زاهدی آغوی</t>
+        </is>
+      </c>
+      <c r="C41" s="49" t="inlineStr">
+        <is>
+          <t>0690489838</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="n">
+        <v>9398000000</v>
+      </c>
+      <c r="E41" s="50" t="n">
+        <v>0.03839820879179247</v>
+      </c>
+      <c r="F41" s="50" t="n">
+        <v>0.9405</v>
+      </c>
+      <c r="G41" s="51" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="H41" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="I41" s="11" t="inlineStr">
         <is>
           <t>پرریسک</t>
         </is>
       </c>
-      <c r="J33" s="8" t="inlineStr">
-        <is>
-          <t>توقف افزایش اعتبار، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>محمد رفیق طرقی</t>
-        </is>
-      </c>
-      <c r="C34" s="49" t="inlineStr">
-        <is>
-          <t>0890543331</t>
-        </is>
-      </c>
-      <c r="D34" s="14" t="n">
-        <v>40300000000</v>
-      </c>
-      <c r="E34" s="50" t="n">
-        <v>0.1646571413395655</v>
-      </c>
-      <c r="F34" s="50" t="n">
-        <v>0.5857</v>
-      </c>
-      <c r="G34" s="51" t="n">
-        <v>271.12</v>
-      </c>
-      <c r="H34" s="10" t="n">
-        <v>78</v>
-      </c>
-      <c r="I34" s="11" t="inlineStr">
+      <c r="J41" s="12" t="inlineStr">
+        <is>
+          <t>مسدودسازی سقف تسهیلات، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>وحید اشرافیان</t>
+        </is>
+      </c>
+      <c r="C42" s="52" t="inlineStr">
+        <is>
+          <t>0921320711</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="n">
+        <v>6247000000</v>
+      </c>
+      <c r="E42" s="53" t="n">
+        <v>0.02552389980020511</v>
+      </c>
+      <c r="F42" s="53" t="n">
+        <v>0.966</v>
+      </c>
+      <c r="G42" s="54" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
         <is>
           <t>پرریسک</t>
         </is>
       </c>
-      <c r="J34" s="12" t="inlineStr">
-        <is>
-          <t>توقف افزایش اعتبار، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>محمدجواد وفادار عیدگاهی</t>
-        </is>
-      </c>
-      <c r="C35" s="52" t="inlineStr">
-        <is>
-          <t>0924020865</t>
-        </is>
-      </c>
-      <c r="D35" s="13" t="n">
-        <v>21630000000</v>
-      </c>
-      <c r="E35" s="53" t="n">
-        <v>0.08837553268423827</v>
-      </c>
-      <c r="F35" s="53" t="n">
-        <v>0.674</v>
-      </c>
-      <c r="G35" s="54" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="H35" s="6" t="n">
-        <v>78</v>
-      </c>
-      <c r="I35" s="7" t="inlineStr">
-        <is>
-          <t>پرریسک</t>
-        </is>
-      </c>
-      <c r="J35" s="8" t="inlineStr">
-        <is>
-          <t>توقف افزایش اعتبار، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>محمد ضیافتی مالدار</t>
-        </is>
-      </c>
-      <c r="C36" s="49" t="inlineStr">
-        <is>
-          <t>0922236992</t>
-        </is>
-      </c>
-      <c r="D36" s="14" t="n">
-        <v>19160000000</v>
-      </c>
-      <c r="E36" s="50" t="n">
-        <v>0.07828364337632941</v>
-      </c>
-      <c r="F36" s="50" t="n">
-        <v>0.7523000000000001</v>
-      </c>
-      <c r="G36" s="51" t="n">
-        <v>61.28</v>
-      </c>
-      <c r="H36" s="10" t="n">
-        <v>72</v>
-      </c>
-      <c r="I36" s="11" t="inlineStr">
-        <is>
-          <t>پرریسک</t>
-        </is>
-      </c>
-      <c r="J36" s="12" t="inlineStr">
-        <is>
-          <t>توقف افزایش اعتبار، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>ابوالفضل شافعی</t>
-        </is>
-      </c>
-      <c r="C37" s="52" t="inlineStr">
-        <is>
-          <t>0941987231</t>
-        </is>
-      </c>
-      <c r="D37" s="13" t="n">
-        <v>12800000000</v>
-      </c>
-      <c r="E37" s="53" t="n">
-        <v>0.05229804985475034</v>
-      </c>
-      <c r="F37" s="53" t="n">
-        <v>0.8046</v>
-      </c>
-      <c r="G37" s="54" t="n">
-        <v>27.35</v>
-      </c>
-      <c r="H37" s="6" t="n">
-        <v>72</v>
-      </c>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>پرریسک</t>
-        </is>
-      </c>
-      <c r="J37" s="8" t="inlineStr">
-        <is>
-          <t>توقف افزایش اعتبار، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="B38" s="12" t="inlineStr">
-        <is>
-          <t>زهرا بهرامی پویا</t>
-        </is>
-      </c>
-      <c r="C38" s="49" t="inlineStr">
-        <is>
-          <t>0927624011</t>
-        </is>
-      </c>
-      <c r="D38" s="14" t="n">
-        <v>12300000000</v>
-      </c>
-      <c r="E38" s="50" t="n">
-        <v>0.05025515728229915</v>
-      </c>
-      <c r="F38" s="50" t="n">
-        <v>0.8549</v>
-      </c>
-      <c r="G38" s="51" t="n">
-        <v>25.26</v>
-      </c>
-      <c r="H38" s="10" t="n">
-        <v>72</v>
-      </c>
-      <c r="I38" s="11" t="inlineStr">
-        <is>
-          <t>پرریسک</t>
-        </is>
-      </c>
-      <c r="J38" s="12" t="inlineStr">
-        <is>
-          <t>توقف افزایش اعتبار، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>احمد زحمتکش باجگیران</t>
-        </is>
-      </c>
-      <c r="C39" s="52" t="inlineStr">
-        <is>
-          <t>0860270361</t>
-        </is>
-      </c>
-      <c r="D39" s="13" t="n">
-        <v>11550000000</v>
-      </c>
-      <c r="E39" s="53" t="n">
-        <v>0.04719081842362238</v>
-      </c>
-      <c r="F39" s="53" t="n">
-        <v>0.9020999999999999</v>
-      </c>
-      <c r="G39" s="54" t="n">
-        <v>22.27</v>
-      </c>
-      <c r="H39" s="6" t="n">
-        <v>72</v>
-      </c>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>پرریسک</t>
-        </is>
-      </c>
-      <c r="J39" s="8" t="inlineStr">
-        <is>
-          <t>توقف افزایش اعتبار، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B40" s="12" t="inlineStr">
-        <is>
-          <t>محمد زاهدی آغوی</t>
-        </is>
-      </c>
-      <c r="C40" s="49" t="inlineStr">
-        <is>
-          <t>0690489838</t>
-        </is>
-      </c>
-      <c r="D40" s="14" t="n">
-        <v>9398000000</v>
-      </c>
-      <c r="E40" s="50" t="n">
-        <v>0.03839820879179247</v>
-      </c>
-      <c r="F40" s="50" t="n">
-        <v>0.9405</v>
-      </c>
-      <c r="G40" s="51" t="n">
-        <v>14.74</v>
-      </c>
-      <c r="H40" s="10" t="n">
-        <v>65</v>
-      </c>
-      <c r="I40" s="11" t="inlineStr">
-        <is>
-          <t>پرریسک</t>
-        </is>
-      </c>
-      <c r="J40" s="12" t="inlineStr">
-        <is>
-          <t>توقف افزایش اعتبار، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>وحید اشرافیان</t>
-        </is>
-      </c>
-      <c r="C41" s="52" t="inlineStr">
-        <is>
-          <t>0921320711</t>
-        </is>
-      </c>
-      <c r="D41" s="13" t="n">
-        <v>6247000000</v>
-      </c>
-      <c r="E41" s="53" t="n">
-        <v>0.02552389980020511</v>
-      </c>
-      <c r="F41" s="53" t="n">
-        <v>0.966</v>
-      </c>
-      <c r="G41" s="54" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="H41" s="6" t="n">
-        <v>65</v>
-      </c>
-      <c r="I41" s="7" t="inlineStr">
-        <is>
-          <t>پرریسک</t>
-        </is>
-      </c>
-      <c r="J41" s="8" t="inlineStr">
-        <is>
-          <t>توقف افزایش اعتبار، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>بهبود جزئی؛ تثبیت و انسداد سقف، ادامه تضمین و پایش روزانه.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="55" t="inlineStr">
+        <is>
+          <t>مجموع ۱۰ صادرکننده اول</t>
+        </is>
+      </c>
+      <c r="B43" s="56" t="n"/>
+      <c r="C43" s="56" t="n"/>
+      <c r="D43" s="46">
+        <f>SUM(D33:D42)</f>
+        <v/>
+      </c>
+      <c r="E43" s="57">
+        <f>SUM(E33:E42)</f>
+        <v/>
+      </c>
+      <c r="F43" s="57">
+        <f>F42</f>
+        <v/>
+      </c>
+      <c r="G43" s="58">
+        <f>SUM(G33:G42)</f>
+        <v/>
+      </c>
+      <c r="H43" s="56" t="n"/>
+      <c r="I43" s="56" t="n"/>
+      <c r="J43" s="59" t="inlineStr">
+        <is>
+          <t>تمرکز ۹۶.۶۰٪ کل برگشتی در ۱۰ مشتری اول</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A31:J31"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A19:D20"/>
   </mergeCells>
@@ -2039,9 +2119,9 @@
           <t>مفهوم اقتصادی و تاثیر در تصمیم اعتباری</t>
         </is>
       </c>
-      <c r="E11" s="95" t="n"/>
-      <c r="F11" s="95" t="n"/>
-      <c r="G11" s="95" t="n"/>
+      <c r="E11" s="92" t="n"/>
+      <c r="F11" s="92" t="n"/>
+      <c r="G11" s="92" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -2064,9 +2144,9 @@
           <t>مستقیم‌ترین شاخص نکول صادرکننده در کل شبکه بانکی کشور</t>
         </is>
       </c>
-      <c r="E12" s="95" t="n"/>
-      <c r="F12" s="95" t="n"/>
-      <c r="G12" s="95" t="n"/>
+      <c r="E12" s="92" t="n"/>
+      <c r="F12" s="92" t="n"/>
+      <c r="G12" s="92" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -2089,9 +2169,9 @@
           <t>سنجش مزمن بودن یا موقت بودن نوسان نقدینگی صادرکننده</t>
         </is>
       </c>
-      <c r="E13" s="95" t="n"/>
-      <c r="F13" s="95" t="n"/>
-      <c r="G13" s="95" t="n"/>
+      <c r="E13" s="92" t="n"/>
+      <c r="F13" s="92" t="n"/>
+      <c r="G13" s="92" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -2114,9 +2194,9 @@
           <t>کشف شوک‌های جدید نقدینگی و انتقال تعهدات در راه به برگشتی</t>
         </is>
       </c>
-      <c r="E14" s="95" t="n"/>
-      <c r="F14" s="95" t="n"/>
-      <c r="G14" s="95" t="n"/>
+      <c r="E14" s="92" t="n"/>
+      <c r="F14" s="92" t="n"/>
+      <c r="G14" s="92" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
@@ -2139,9 +2219,9 @@
           <t>ارزیابی توان بازپرداخت بدهی نسبت به حجم گردش مالی</t>
         </is>
       </c>
-      <c r="E15" s="95" t="n"/>
-      <c r="F15" s="95" t="n"/>
-      <c r="G15" s="95" t="n"/>
+      <c r="E15" s="92" t="n"/>
+      <c r="F15" s="92" t="n"/>
+      <c r="G15" s="92" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -2164,9 +2244,9 @@
           <t>هشدار انباشت تعهدات آتی و احتمال عدم وصول در سررسید</t>
         </is>
       </c>
-      <c r="E16" s="95" t="n"/>
-      <c r="F16" s="95" t="n"/>
-      <c r="G16" s="95" t="n"/>
+      <c r="E16" s="92" t="n"/>
+      <c r="F16" s="92" t="n"/>
+      <c r="G16" s="92" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
@@ -2189,9 +2269,9 @@
           <t>بی‌انضباطی مالی و رفتارهای پیش‌بینی‌ناپذیر صادرکننده</t>
         </is>
       </c>
-      <c r="E17" s="95" t="n"/>
-      <c r="F17" s="95" t="n"/>
-      <c r="G17" s="95" t="n"/>
+      <c r="E17" s="92" t="n"/>
+      <c r="F17" s="92" t="n"/>
+      <c r="G17" s="92" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -2214,9 +2294,9 @@
           <t>کاهش اطمینان اعتباری ناشی از عدم شفافیت سوابق هویتی</t>
         </is>
       </c>
-      <c r="E18" s="95" t="n"/>
-      <c r="F18" s="95" t="n"/>
-      <c r="G18" s="95" t="n"/>
+      <c r="E18" s="92" t="n"/>
+      <c r="F18" s="92" t="n"/>
+      <c r="G18" s="92" t="n"/>
     </row>
     <row r="19"/>
     <row r="20">
@@ -2252,127 +2332,127 @@
           <t>اقدام اعتباری سامانه‌ای</t>
         </is>
       </c>
-      <c r="F21" s="95" t="n"/>
-      <c r="G21" s="95" t="n"/>
+      <c r="F21" s="92" t="n"/>
+      <c r="G21" s="92" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="93" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B22" s="96" t="inlineStr">
+      <c r="B22" s="94" t="inlineStr">
         <is>
           <t>برگشتی &gt; ۵۰ میلیارد ریال و پایدار (&gt;= ۳ دوره)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="93" t="inlineStr">
         <is>
           <t>حداقل ۸۵</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="93" t="inlineStr">
         <is>
           <t>اقدام فوری (Immediate Action)</t>
         </is>
       </c>
-      <c r="E22" s="25" t="inlineStr">
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>انسداد فوری حساب، ضبط وثایق و وصول آنی (مانند حسین حشمتی)</t>
         </is>
       </c>
-      <c r="F22" s="95" t="n"/>
-      <c r="G22" s="95" t="n"/>
+      <c r="F22" s="92" t="n"/>
+      <c r="G22" s="92" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="28" t="inlineStr">
+      <c r="A23" s="95" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="B23" s="97" t="inlineStr">
+      <c r="B23" s="96" t="inlineStr">
         <is>
           <t>برگشتی &gt; ۲۰ میلیارد ریال و پایدار (&gt;= ۳ دوره)</t>
         </is>
       </c>
-      <c r="C23" s="28" t="inlineStr">
+      <c r="C23" s="95" t="inlineStr">
         <is>
           <t>حداقل ۷۸</t>
         </is>
       </c>
-      <c r="D23" s="28" t="inlineStr">
+      <c r="D23" s="95" t="inlineStr">
         <is>
           <t>پرریسک (High Risk)</t>
         </is>
       </c>
-      <c r="E23" s="31" t="inlineStr">
+      <c r="E23" s="29" t="inlineStr">
         <is>
           <t>توقف افزایش اعتبار، اخذ وثایق ملکی یا نقد (زوار، طرقی، وفادار)</t>
         </is>
       </c>
-      <c r="F23" s="95" t="n"/>
-      <c r="G23" s="95" t="n"/>
+      <c r="F23" s="92" t="n"/>
+      <c r="G23" s="92" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="28" t="inlineStr">
+      <c r="A24" s="95" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
       </c>
-      <c r="B24" s="97" t="inlineStr">
+      <c r="B24" s="96" t="inlineStr">
         <is>
           <t>برگشتی &gt; ۱۰ میلیارد ریال و پایدار (&gt;= ۳ دوره)</t>
         </is>
       </c>
-      <c r="C24" s="28" t="inlineStr">
+      <c r="C24" s="95" t="inlineStr">
         <is>
           <t>حداقل ۷۲</t>
         </is>
       </c>
-      <c r="D24" s="28" t="inlineStr">
+      <c r="D24" s="95" t="inlineStr">
         <is>
           <t>پرریسک (High Risk)</t>
         </is>
       </c>
-      <c r="E24" s="31" t="inlineStr">
+      <c r="E24" s="29" t="inlineStr">
         <is>
           <t>کاهش سقف اعتباری و اخذ تضمین تکمیلی (ضیافتی، زحمتکش)</t>
         </is>
       </c>
-      <c r="F24" s="95" t="n"/>
-      <c r="G24" s="95" t="n"/>
+      <c r="F24" s="92" t="n"/>
+      <c r="G24" s="92" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="28" t="inlineStr">
+      <c r="A25" s="95" t="inlineStr">
         <is>
           <t>F4</t>
         </is>
       </c>
-      <c r="B25" s="97" t="inlineStr">
+      <c r="B25" s="96" t="inlineStr">
         <is>
           <t>برگشتی &gt; ۵ میلیارد ریال و پایدار (&gt;= ۳ دوره)</t>
         </is>
       </c>
-      <c r="C25" s="28" t="inlineStr">
+      <c r="C25" s="95" t="inlineStr">
         <is>
           <t>حداقل ۶۵</t>
         </is>
       </c>
-      <c r="D25" s="28" t="inlineStr">
+      <c r="D25" s="95" t="inlineStr">
         <is>
           <t>پرریسک (High Risk)</t>
         </is>
       </c>
-      <c r="E25" s="31" t="inlineStr">
+      <c r="E25" s="29" t="inlineStr">
         <is>
           <t>کنترل وصولی‌ها قبل از سررسید (زاهدی، اشرافیان)</t>
         </is>
       </c>
-      <c r="F25" s="95" t="n"/>
-      <c r="G25" s="95" t="n"/>
+      <c r="F25" s="92" t="n"/>
+      <c r="G25" s="92" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="34" t="inlineStr">
+      <c r="A26" s="97" t="inlineStr">
         <is>
           <t>F5</t>
         </is>
@@ -2382,52 +2462,52 @@
           <t>برگشتی مثبت (&gt; ۰) و پایدار (&gt;= ۳ دوره)</t>
         </is>
       </c>
-      <c r="C26" s="34" t="inlineStr">
+      <c r="C26" s="97" t="inlineStr">
         <is>
           <t>حداقل ۴۵</t>
         </is>
       </c>
-      <c r="D26" s="34" t="inlineStr">
+      <c r="D26" s="97" t="inlineStr">
         <is>
           <t>مراقبت (Watch List)</t>
         </is>
       </c>
-      <c r="E26" s="37" t="inlineStr">
+      <c r="E26" s="34" t="inlineStr">
         <is>
           <t>ورود به فهرست تحت‌نظر و اخذ چک تضمین جدید (موسوی، محمدی)</t>
         </is>
       </c>
-      <c r="F26" s="95" t="n"/>
-      <c r="G26" s="95" t="n"/>
+      <c r="F26" s="92" t="n"/>
+      <c r="G26" s="92" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="40" t="inlineStr">
+      <c r="A27" s="99" t="inlineStr">
         <is>
           <t>F6</t>
         </is>
       </c>
-      <c r="B27" s="99" t="inlineStr">
+      <c r="B27" s="100" t="inlineStr">
         <is>
           <t>برگشتی جدید غیرپایدار (۱ تا ۲ دوره)</t>
         </is>
       </c>
-      <c r="C27" s="40" t="inlineStr">
+      <c r="C27" s="99" t="inlineStr">
         <is>
           <t>حداقل ۳۵</t>
         </is>
       </c>
-      <c r="D27" s="40" t="inlineStr">
+      <c r="D27" s="99" t="inlineStr">
         <is>
           <t>عادی / آستانه مراقبت</t>
         </is>
       </c>
-      <c r="E27" s="38" t="inlineStr">
+      <c r="E27" s="35" t="inlineStr">
         <is>
           <t>پایش دقیق و بررسی علت نکول موقت (زهرا بهرامی پویا)</t>
         </is>
       </c>
-      <c r="F27" s="95" t="n"/>
-      <c r="G27" s="95" t="n"/>
+      <c r="F27" s="92" t="n"/>
+      <c r="G27" s="92" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -2473,7 +2553,7 @@
     <col width="65" customWidth="1" min="1" max="1"/>
     <col width="37" customWidth="1" min="2" max="2"/>
     <col width="51" customWidth="1" min="3" max="3"/>
-    <col width="51" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
     <col width="41" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
@@ -2540,12 +2620,12 @@
           <t>واحد تحلیل و مبنای تجمیع</t>
         </is>
       </c>
-      <c r="C5" s="100" t="inlineStr">
+      <c r="C5" s="101" t="inlineStr">
         <is>
           <t>ردیف‌های چک و ادغام‌های نامعتبر</t>
         </is>
       </c>
-      <c r="D5" s="69" t="inlineStr">
+      <c r="D5" s="67" t="inlineStr">
         <is>
           <t>صادرکننده/مشتری یکتا (کدملی ۱۰ رقمی)</t>
         </is>
@@ -2575,12 +2655,12 @@
           <t>تعداد پروفایل‌های بانکی معتبر</t>
         </is>
       </c>
-      <c r="C6" s="101" t="inlineStr">
+      <c r="C6" s="102" t="inlineStr">
         <is>
           <t>۴۸ یا ۵۲ ردیف با پرونده‌های نامعتبر</t>
         </is>
       </c>
-      <c r="D6" s="102" t="inlineStr">
+      <c r="D6" s="103" t="inlineStr">
         <is>
           <t>دقیقاً ۴۶ پروفایل بانکی معتبر یکتا</t>
         </is>
@@ -2610,12 +2690,12 @@
           <t>مجموع چک‌های در راه بانکی</t>
         </is>
       </c>
-      <c r="C7" s="100" t="inlineStr">
+      <c r="C7" s="101" t="inlineStr">
         <is>
           <t>۴,۴۶۶,۰۶۹,۴۶۹,۴۵۴ ریال</t>
         </is>
       </c>
-      <c r="D7" s="69" t="inlineStr">
+      <c r="D7" s="67" t="inlineStr">
         <is>
           <t>۴,۸۵۶,۳۲۲,۰۵۱,۴۰۷ ریال</t>
         </is>
@@ -2645,12 +2725,12 @@
           <t>مجموع چک‌های برگشتی بانکی</t>
         </is>
       </c>
-      <c r="C8" s="101" t="inlineStr">
+      <c r="C8" s="102" t="inlineStr">
         <is>
           <t>۲۳۱,۹۵۱,۰۰۰,۰۰۰ ریال</t>
         </is>
       </c>
-      <c r="D8" s="102" t="inlineStr">
+      <c r="D8" s="103" t="inlineStr">
         <is>
           <t>۲۴۴,۷۵۱,۰۰۰,۰۰۰ ریال</t>
         </is>
@@ -2680,12 +2760,12 @@
           <t>مجموع مبالغ رفع سوءاثر بانکی</t>
         </is>
       </c>
-      <c r="C9" s="100" t="inlineStr">
+      <c r="C9" s="101" t="inlineStr">
         <is>
           <t>۱,۰۲۴,۳۰۵,۱۸۵,۷۹۷ ریال</t>
         </is>
       </c>
-      <c r="D9" s="69" t="inlineStr">
+      <c r="D9" s="67" t="inlineStr">
         <is>
           <t>۱,۱۰۹,۴۸۶,۹۹۹,۹۶۸ ریال</t>
         </is>
@@ -2715,12 +2795,12 @@
           <t>تعهد فعال بانکی (در راه + برگشتی)</t>
         </is>
       </c>
-      <c r="C10" s="101" t="inlineStr">
+      <c r="C10" s="102" t="inlineStr">
         <is>
           <t>۴,۶۹۸,۰۲۰,۴۶۹,۴۵۴ ریال</t>
         </is>
       </c>
-      <c r="D10" s="102" t="inlineStr">
+      <c r="D10" s="103" t="inlineStr">
         <is>
           <t>۵,۱۰۱,۰۷۳,۰۵۱,۴۰۷ ریال</t>
         </is>
@@ -2750,12 +2830,12 @@
           <t>ارزش ریالی چک‌های صندوق معتبر</t>
         </is>
       </c>
-      <c r="C11" s="100" t="inlineStr">
+      <c r="C11" s="101" t="inlineStr">
         <is>
           <t>۴۸۳,۳۲۵,۰۰۰,۰۰۰ ریال (بدون تفکیک)</t>
         </is>
       </c>
-      <c r="D11" s="69" t="inlineStr">
+      <c r="D11" s="67" t="inlineStr">
         <is>
           <t>۴۷۹,۷۰۵,۰۰۰,۰۰۰ ریال</t>
         </is>
@@ -2785,12 +2865,12 @@
           <t>پرونده ابوالفضل شافعی (کد ۵)</t>
         </is>
       </c>
-      <c r="C12" s="101" t="inlineStr">
+      <c r="C12" s="102" t="inlineStr">
         <is>
           <t>برگشتی صفر و فاقد رخداد انتقال</t>
         </is>
       </c>
-      <c r="D12" s="102" t="inlineStr">
+      <c r="D12" s="103" t="inlineStr">
         <is>
           <t>برگشتی ۱۲.۸B و انتقال قطعی ۷.۵B</t>
         </is>
@@ -2820,12 +2900,12 @@
           <t>پرونده زهرا بهرامی پویا (کد ۴۶)</t>
         </is>
       </c>
-      <c r="C13" s="100" t="inlineStr">
+      <c r="C13" s="101" t="inlineStr">
         <is>
           <t>نمره پایین / عدم اعمال کف اجباری</t>
         </is>
       </c>
-      <c r="D13" s="69" t="inlineStr">
+      <c r="D13" s="67" t="inlineStr">
         <is>
           <t>برگشتی ۱۲.۳B، انتقال ۳.۵B، نمره &gt;= ۷۲</t>
         </is>
@@ -2855,12 +2935,12 @@
           <t>احراز هویت طاهری (کد ۷)</t>
         </is>
       </c>
-      <c r="C14" s="101" t="inlineStr">
+      <c r="C14" s="102" t="inlineStr">
         <is>
           <t>فاقد کد ملی با نام ساختگی «مسعود قدیری»</t>
         </is>
       </c>
-      <c r="D14" s="102" t="inlineStr">
+      <c r="D14" s="103" t="inlineStr">
         <is>
           <t>کدملی 6510019418 با وضعیت VERIFIED</t>
         </is>
@@ -2877,7 +2957,7 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>پالایش دیتابیس، استعلام کد ملی و تایید اعتباری؛ انطباق با AUD-11</t>
+          <t>بازیابی از سابقه معتبر داخلی/شناسه صیاد تاریخی؛ انطباق با AUD-11</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2970,12 @@
           <t>احراز هویت فرهنگ‌نیا (کد ۱۳)</t>
         </is>
       </c>
-      <c r="C15" s="100" t="inlineStr">
+      <c r="C15" s="101" t="inlineStr">
         <is>
           <t>فاقد شناسه با نام «بازرگانی مانی بارثاوا»</t>
         </is>
       </c>
-      <c r="D15" s="69" t="inlineStr">
+      <c r="D15" s="67" t="inlineStr">
         <is>
           <t>کدملی 2110152184 با وضعیت VERIFIED</t>
         </is>
@@ -2912,7 +2992,7 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>ثبت کدملی مهزیار فرهنگ‌نیا و استعلام سوابق؛ انطباق با AUD-11</t>
+          <t>بازیابی از سابقه معتبر داخلی/شناسه صیاد تاریخی؛ انطباق با AUD-11</t>
         </is>
       </c>
     </row>
@@ -2925,12 +3005,12 @@
           <t>احراز هویت ضرغام‌مقدم (کد ۲۶)</t>
         </is>
       </c>
-      <c r="C16" s="101" t="inlineStr">
+      <c r="C16" s="102" t="inlineStr">
         <is>
           <t>کدملی مفقود با نام «امیر هوشنگ حامدی‌نسب»</t>
         </is>
       </c>
-      <c r="D16" s="102" t="inlineStr">
+      <c r="D16" s="103" t="inlineStr">
         <is>
           <t>کدملی 0941876578 با وضعیت VERIFIED</t>
         </is>
@@ -2942,12 +3022,12 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>تولید نام فرضی غیرمنطبق با ثبت احوال</t>
+          <t>تولید نام فرضی غیرمنطبق با اسناد صندوق</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>ثبت کدملی علیرضا ضرغام‌مقدم و استعلام سوابق؛ انطباق با AUD-11</t>
+          <t>بازیابی از سابقه معتبر داخلی/شناسه صیاد تاریخی؛ انطباق با AUD-11</t>
         </is>
       </c>
     </row>
@@ -2960,12 +3040,12 @@
           <t>پرونده داوود رنگرززاده (کد ۲۹)</t>
         </is>
       </c>
-      <c r="C17" s="100" t="inlineStr">
+      <c r="C17" s="101" t="inlineStr">
         <is>
           <t>نام ساختگی «برادران عسگری» (حساب مشترک)</t>
         </is>
       </c>
-      <c r="D17" s="69" t="inlineStr">
+      <c r="D17" s="67" t="inlineStr">
         <is>
           <t>نام واقعی داوود رنگرززاده (UNRESOLVED)</t>
         </is>
@@ -2995,12 +3075,12 @@
           <t>پرونده عباس مقنی (کد ۱۷)</t>
         </is>
       </c>
-      <c r="C18" s="101" t="inlineStr">
+      <c r="C18" s="102" t="inlineStr">
         <is>
           <t>ثبت کاذب رخداد رفع سوءاثر با صفر شدن ارقام</t>
         </is>
       </c>
-      <c r="D18" s="102" t="inlineStr">
+      <c r="D18" s="103" t="inlineStr">
         <is>
           <t>حفظ مقادیر معتبر، صفر رخداد کاذب در شیت ۳</t>
         </is>
@@ -3030,14 +3110,14 @@
           <t>پرونده جواد غفوریان (کد ۱۱)</t>
         </is>
       </c>
-      <c r="C19" s="100" t="inlineStr">
+      <c r="C19" s="101" t="inlineStr">
         <is>
           <t>قرارگیری در طبقه کم‌ریسک بدون پایش</t>
         </is>
       </c>
-      <c r="D19" s="69" t="inlineStr">
-        <is>
-          <t>تسویه ۱۰B، افزایش ۱۰B رفع اثر، طبقه مراقبت</t>
+      <c r="D19" s="67" t="inlineStr">
+        <is>
+          <t>تسویه ۱B، افزایش ۱B رفع اثر (کاهش ۱,۰۰۰,۰۰۰,۰۰۰ ریال برگشتی)، طبقه مراقبت</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
@@ -3047,12 +3127,12 @@
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>عدم لحاظ دوره گذار پایش پس از تسویه بزرگ</t>
+          <t>عدم لحاظ دوره گذار پایش پس از تسویه</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>تخصیص کف دوره گذار ۴۵ و ثبت در شیت مراقبت و بهبود</t>
+          <t>تخصیص کف دوره گذار ۴۵ و ثبت در شیت مراقبت و بهبود؛ پایش روزانه الزامی</t>
         </is>
       </c>
     </row>
@@ -3065,12 +3145,12 @@
           <t>پاکسازی اسامی ساختگی (شیت ۸)</t>
         </is>
       </c>
-      <c r="C20" s="101" t="inlineStr">
+      <c r="C20" s="102" t="inlineStr">
         <is>
           <t>وجود قدیری، بارثاوا، حامدی‌نسب، عسگری، نجارزاده</t>
         </is>
       </c>
-      <c r="D20" s="102" t="inlineStr">
+      <c r="D20" s="103" t="inlineStr">
         <is>
           <t>صفر نام ساختگی؛ صرفاً اسناد واقعی با شناسه منشأ</t>
         </is>
@@ -3100,19 +3180,19 @@
           <t>سیستم ممیزی مستقل (شیت ۹)</t>
         </is>
       </c>
-      <c r="C21" s="100" t="inlineStr">
+      <c r="C21" s="101" t="inlineStr">
         <is>
           <t>۱۰ آزمون اولیه با فرمول‌های غیرمنطبق</t>
         </is>
       </c>
-      <c r="D21" s="69" t="inlineStr">
-        <is>
-          <t>۱۴ آزمون ممیزی رسمی خودکار با نتیجه ۱۰۰٪ PASS</t>
+      <c r="D21" s="67" t="inlineStr">
+        <is>
+          <t>۱۹ آزمون ممیزی رسمی خودکار (AUD-01 تا AUD-19) با نتیجه ۱۰۰٪ PASS</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>+۴ آزمون تکمیلی کنترلی</t>
+          <t>+۹ آزمون تکمیلی کنترلی و رفتاری</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -3122,16 +3202,16 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>پیاده‌سازی ۱۴ آزمون قطعی AUD-01 تا AUD-14 با فرمول‌های اکسل؛ ۱۰۰٪ PASS</t>
+          <t>پیاده‌سازی ۱۹ آزمون قطعی AUD-01 تا AUD-19 با فرمول‌های اکسل؛ ۱۰۰٪ PASS</t>
         </is>
       </c>
     </row>
     <row r="22"/>
     <row r="23">
-      <c r="A23" s="103" t="inlineStr">
+      <c r="A23" s="104" t="inlineStr">
         <is>
           <t>تاییدیه مدیر ارشد سیستم و ناظر مستقل اعتباری:
-«کلیه مغایرت‌های فوق بر اساس استعلام‌های قطعی سامانه صیاد بانک مرکزی، دفاتر فیزیکی اسناد صندوق و ممیزی مستقل ریاضی برطرف گردیده و نسخه حاضر، سند مرجع قطعی تصمیم‌گیری اعتباری می‌باشد.»</t>
+«کلیه مغایرت‌های فوق بر اساس بازیابی از سابقه معتبر داخلی/شناسه صیاد تاریخی، دفاتر فیزیکی اسناد صندوق و ممیزی مستقل ریاضی ۱۹ آزمونه برطرف گردیده و نسخه حاضر، سند مرجع قطعی تصمیم‌گیری اعتباری می‌باشد.»</t>
         </is>
       </c>
       <c r="B23" s="18" t="n"/>
@@ -3349,29 +3429,29 @@
       </c>
       <c r="M4" s="7" t="inlineStr">
         <is>
-          <t>CHRONIC</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="N4" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="O4" s="55" t="n">
-        <v>62.77</v>
+        <v>2</v>
+      </c>
+      <c r="O4" s="16" t="n">
+        <v>50.77</v>
       </c>
       <c r="P4" s="7" t="n">
         <v>85</v>
       </c>
-      <c r="Q4" s="55" t="n">
+      <c r="Q4" s="16" t="n">
         <v>85</v>
       </c>
-      <c r="R4" s="56" t="inlineStr">
+      <c r="R4" s="60" t="inlineStr">
         <is>
           <t>اقدام فوری</t>
         </is>
       </c>
       <c r="S4" s="8" t="inlineStr">
         <is>
-          <t>توقف فوری تخصیص اعتبار، مطالبه وثیقه ملکی/نقدی، اقدام حقوقی و وصول آنی.</t>
+          <t>مسدودسازی کامل تسهیلات، مطالبه وثیقه ملکی/نقدی، اقدام حقوقی و وصول آنی.</t>
         </is>
       </c>
     </row>
@@ -3428,23 +3508,23 @@
       <c r="N5" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O5" s="57" t="n">
+      <c r="O5" s="61" t="n">
         <v>31.74</v>
       </c>
       <c r="P5" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="Q5" s="57" t="n">
+      <c r="Q5" s="61" t="n">
         <v>72</v>
       </c>
-      <c r="R5" s="58" t="inlineStr">
+      <c r="R5" s="62" t="inlineStr">
         <is>
           <t>پرریسک</t>
         </is>
       </c>
       <c r="S5" s="12" t="inlineStr">
         <is>
-          <t>توقف افزایش اعتبار، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
+          <t>مسدودسازی سقف تسهیلات، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
         </is>
       </c>
     </row>
@@ -3495,29 +3575,29 @@
       </c>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>INTERMITTENT</t>
+          <t>CHRONIC</t>
         </is>
       </c>
       <c r="N6" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="O6" s="55" t="n">
-        <v>18.87</v>
+        <v>6</v>
+      </c>
+      <c r="O6" s="16" t="n">
+        <v>20.87</v>
       </c>
       <c r="P6" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="Q6" s="55" t="n">
+      <c r="Q6" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="R6" s="59" t="inlineStr">
+      <c r="R6" s="63" t="inlineStr">
         <is>
           <t>مراقبت</t>
         </is>
       </c>
       <c r="S6" s="8" t="inlineStr">
         <is>
-          <t>پایش هفتگی، اخذ تضمین مضاعف، عدم پذیرش چک جدید با سررسید بالای ۳۰ روز.</t>
+          <t>داده تاریخی؛ مسدودسازی سقف تسهیلات و پایش روزانه تا دریافت استعلام معتبر جدید.</t>
         </is>
       </c>
     </row>
@@ -3568,29 +3648,29 @@
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>INTERMITTENT</t>
+          <t>CHRONIC</t>
         </is>
       </c>
       <c r="N7" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="O7" s="57" t="n">
-        <v>34.62</v>
+        <v>10</v>
+      </c>
+      <c r="O7" s="61" t="n">
+        <v>46.62</v>
       </c>
       <c r="P7" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="Q7" s="57" t="n">
+      <c r="Q7" s="61" t="n">
         <v>72</v>
       </c>
-      <c r="R7" s="58" t="inlineStr">
+      <c r="R7" s="62" t="inlineStr">
         <is>
           <t>پرریسک</t>
         </is>
       </c>
       <c r="S7" s="12" t="inlineStr">
         <is>
-          <t>توقف افزایش اعتبار، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
+          <t>مسدودسازی سقف تسهیلات، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3727,7 @@
       <c r="N8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O8" s="55" t="n">
+      <c r="O8" s="16" t="n">
         <v>0.16</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
@@ -3655,17 +3735,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q8" s="55" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R8" s="60" t="inlineStr">
+      <c r="Q8" s="16" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="R8" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3802,7 @@
       <c r="N9" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="57" t="n">
+      <c r="O9" s="61" t="n">
         <v>0</v>
       </c>
       <c r="P9" s="11" t="inlineStr">
@@ -3730,17 +3810,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q9" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="60" t="inlineStr">
+      <c r="Q9" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S9" s="12" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3877,7 @@
       <c r="N10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O10" s="55" t="n">
+      <c r="O10" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
@@ -3805,17 +3885,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q10" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="60" t="inlineStr">
+      <c r="Q10" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S10" s="8" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -3872,7 +3952,7 @@
       <c r="N11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="O11" s="57" t="n">
+      <c r="O11" s="61" t="n">
         <v>0</v>
       </c>
       <c r="P11" s="11" t="inlineStr">
@@ -3880,17 +3960,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q11" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="60" t="inlineStr">
+      <c r="Q11" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S11" s="12" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -3947,7 +4027,7 @@
       <c r="N12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="55" t="n">
+      <c r="O12" s="16" t="n">
         <v>2.33</v>
       </c>
       <c r="P12" s="7" t="inlineStr">
@@ -3955,17 +4035,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q12" s="55" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R12" s="60" t="inlineStr">
+      <c r="Q12" s="16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R12" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S12" s="8" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -4016,29 +4096,29 @@
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>INTERMITTENT</t>
         </is>
       </c>
       <c r="N13" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" s="61" t="n">
         <v>0</v>
       </c>
       <c r="P13" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="Q13" s="57" t="n">
+      <c r="Q13" s="61" t="n">
         <v>45</v>
       </c>
-      <c r="R13" s="59" t="inlineStr">
+      <c r="R13" s="63" t="inlineStr">
         <is>
           <t>مراقبت</t>
         </is>
       </c>
       <c r="S13" s="12" t="inlineStr">
         <is>
-          <t>پایش هفتگی، اخذ تضمین مضاعف، عدم پذیرش چک جدید با سررسید بالای ۳۰ روز.</t>
+          <t>رفع سوءاثر کامل ثبت شد؛ دوره گذار پایش و پایش روزانه. هرگونه ارتقای سقف تا تأیید دوره‌های بعدی ممنوع است.</t>
         </is>
       </c>
     </row>
@@ -4095,7 +4175,7 @@
       <c r="N14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="55" t="n">
+      <c r="O14" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P14" s="7" t="inlineStr">
@@ -4103,17 +4183,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q14" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="60" t="inlineStr">
+      <c r="Q14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S14" s="8" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4250,7 @@
       <c r="N15" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="O15" s="57" t="n">
+      <c r="O15" s="61" t="n">
         <v>0</v>
       </c>
       <c r="P15" s="11" t="inlineStr">
@@ -4178,17 +4258,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q15" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="60" t="inlineStr">
+      <c r="Q15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S15" s="12" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -4245,7 +4325,7 @@
       <c r="N16" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O16" s="55" t="n">
+      <c r="O16" s="16" t="n">
         <v>0.04</v>
       </c>
       <c r="P16" s="7" t="inlineStr">
@@ -4253,17 +4333,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q16" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="60" t="inlineStr">
+      <c r="Q16" s="16" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R16" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S16" s="8" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -4318,25 +4398,25 @@
         </is>
       </c>
       <c r="N17" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="O17" s="57" t="n">
-        <v>30.39</v>
+        <v>10</v>
+      </c>
+      <c r="O17" s="61" t="n">
+        <v>32.39</v>
       </c>
       <c r="P17" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="Q17" s="57" t="n">
+      <c r="Q17" s="61" t="n">
         <v>72</v>
       </c>
-      <c r="R17" s="58" t="inlineStr">
+      <c r="R17" s="62" t="inlineStr">
         <is>
           <t>پرریسک</t>
         </is>
       </c>
       <c r="S17" s="12" t="inlineStr">
         <is>
-          <t>توقف افزایش اعتبار، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
+          <t>مسدودسازی سقف تسهیلات، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
         </is>
       </c>
     </row>
@@ -4387,31 +4467,31 @@
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="N18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="55" t="n">
-        <v>0.16</v>
+        <v>2</v>
+      </c>
+      <c r="O18" s="16" t="n">
+        <v>7.11</v>
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q18" s="55" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R18" s="60" t="inlineStr">
+      <c r="Q18" s="16" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="R18" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S18" s="8" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -4466,25 +4546,25 @@
         </is>
       </c>
       <c r="N19" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="O19" s="57" t="n">
-        <v>33.28</v>
+        <v>10</v>
+      </c>
+      <c r="O19" s="61" t="n">
+        <v>52.93</v>
       </c>
       <c r="P19" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="Q19" s="57" t="n">
-        <v>45</v>
-      </c>
-      <c r="R19" s="59" t="inlineStr">
+      <c r="Q19" s="61" t="n">
+        <v>52.93</v>
+      </c>
+      <c r="R19" s="63" t="inlineStr">
         <is>
           <t>مراقبت</t>
         </is>
       </c>
       <c r="S19" s="12" t="inlineStr">
         <is>
-          <t>پایش هفتگی، اخذ تضمین مضاعف، عدم پذیرش چک جدید با سررسید بالای ۳۰ روز.</t>
+          <t>رخداد برگشتی جدید (+۳.۷B)؛ انسداد سقف تسهیلات، اخذ وثیقه و پایش روزانه.</t>
         </is>
       </c>
     </row>
@@ -4535,31 +4615,31 @@
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
-          <t>CHRONIC</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="N20" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="O20" s="55" t="n">
-        <v>4.82</v>
+        <v>0</v>
+      </c>
+      <c r="O20" s="16" t="n">
+        <v>4.95</v>
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q20" s="55" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R20" s="60" t="inlineStr">
+      <c r="Q20" s="16" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="R20" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S20" s="8" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -4614,25 +4694,25 @@
         </is>
       </c>
       <c r="N21" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="O21" s="57" t="n">
-        <v>18.1</v>
+        <v>10</v>
+      </c>
+      <c r="O21" s="61" t="n">
+        <v>24.1</v>
       </c>
       <c r="P21" s="11" t="n">
         <v>65</v>
       </c>
-      <c r="Q21" s="57" t="n">
+      <c r="Q21" s="61" t="n">
         <v>65</v>
       </c>
-      <c r="R21" s="58" t="inlineStr">
+      <c r="R21" s="62" t="inlineStr">
         <is>
           <t>پرریسک</t>
         </is>
       </c>
       <c r="S21" s="12" t="inlineStr">
         <is>
-          <t>توقف افزایش اعتبار، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
+          <t>بهبود جزئی؛ تثبیت و انسداد سقف، ادامه تضمین و پایش روزانه.</t>
         </is>
       </c>
     </row>
@@ -4687,25 +4767,25 @@
         </is>
       </c>
       <c r="N22" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="O22" s="55" t="n">
+        <v>10</v>
+      </c>
+      <c r="O22" s="16" t="n">
         <v>49.89</v>
       </c>
       <c r="P22" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="Q22" s="55" t="n">
+      <c r="Q22" s="16" t="n">
         <v>78</v>
       </c>
-      <c r="R22" s="58" t="inlineStr">
+      <c r="R22" s="62" t="inlineStr">
         <is>
           <t>پرریسک</t>
         </is>
       </c>
       <c r="S22" s="8" t="inlineStr">
         <is>
-          <t>توقف افزایش اعتبار، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
+          <t>مسدودسازی سقف تسهیلات، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
         </is>
       </c>
     </row>
@@ -4762,7 +4842,7 @@
       <c r="N23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="O23" s="57" t="n">
+      <c r="O23" s="61" t="n">
         <v>0</v>
       </c>
       <c r="P23" s="11" t="inlineStr">
@@ -4770,17 +4850,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q23" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" s="60" t="inlineStr">
+      <c r="Q23" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S23" s="12" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -4835,25 +4915,25 @@
         </is>
       </c>
       <c r="N24" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="O24" s="55" t="n">
-        <v>24</v>
+        <v>10</v>
+      </c>
+      <c r="O24" s="16" t="n">
+        <v>28</v>
       </c>
       <c r="P24" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="Q24" s="55" t="n">
+      <c r="Q24" s="16" t="n">
         <v>65</v>
       </c>
-      <c r="R24" s="58" t="inlineStr">
+      <c r="R24" s="62" t="inlineStr">
         <is>
           <t>پرریسک</t>
         </is>
       </c>
       <c r="S24" s="8" t="inlineStr">
         <is>
-          <t>توقف افزایش اعتبار، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
+          <t>مسدودسازی سقف تسهیلات، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4990,7 @@
       <c r="N25" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="O25" s="57" t="n">
+      <c r="O25" s="61" t="n">
         <v>3.65</v>
       </c>
       <c r="P25" s="11" t="inlineStr">
@@ -4918,17 +4998,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q25" s="57" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R25" s="60" t="inlineStr">
+      <c r="Q25" s="61" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R25" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S25" s="12" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -4985,7 +5065,7 @@
       <c r="N26" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O26" s="55" t="n">
+      <c r="O26" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P26" s="7" t="inlineStr">
@@ -4993,17 +5073,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q26" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="60" t="inlineStr">
+      <c r="Q26" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S26" s="8" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5140,7 @@
       <c r="N27" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="O27" s="57" t="n">
+      <c r="O27" s="61" t="n">
         <v>0</v>
       </c>
       <c r="P27" s="11" t="inlineStr">
@@ -5068,17 +5148,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q27" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="60" t="inlineStr">
+      <c r="Q27" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S27" s="12" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5215,7 @@
       <c r="N28" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O28" s="55" t="n">
+      <c r="O28" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P28" s="7" t="inlineStr">
@@ -5143,17 +5223,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q28" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="60" t="inlineStr">
+      <c r="Q28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S28" s="8" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5290,7 @@
       <c r="N29" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="O29" s="57" t="n">
+      <c r="O29" s="61" t="n">
         <v>1.57</v>
       </c>
       <c r="P29" s="11" t="inlineStr">
@@ -5218,17 +5298,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q29" s="57" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R29" s="60" t="inlineStr">
+      <c r="Q29" s="61" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R29" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S29" s="12" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -5285,7 +5365,7 @@
       <c r="N30" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O30" s="55" t="n">
+      <c r="O30" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P30" s="7" t="inlineStr">
@@ -5293,17 +5373,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q30" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="60" t="inlineStr">
+      <c r="Q30" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S30" s="8" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5440,7 @@
       <c r="N31" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="O31" s="57" t="n">
+      <c r="O31" s="61" t="n">
         <v>0</v>
       </c>
       <c r="P31" s="11" t="inlineStr">
@@ -5368,17 +5448,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q31" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="60" t="inlineStr">
+      <c r="Q31" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S31" s="12" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -5435,7 +5515,7 @@
       <c r="N32" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O32" s="55" t="n">
+      <c r="O32" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P32" s="7" t="inlineStr">
@@ -5443,17 +5523,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q32" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="60" t="inlineStr">
+      <c r="Q32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S32" s="8" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5590,7 @@
       <c r="N33" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="O33" s="57" t="n">
+      <c r="O33" s="61" t="n">
         <v>0</v>
       </c>
       <c r="P33" s="11" t="inlineStr">
@@ -5518,17 +5598,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q33" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" s="60" t="inlineStr">
+      <c r="Q33" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S33" s="12" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -5579,31 +5659,31 @@
       </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>INTERMITTENT</t>
         </is>
       </c>
       <c r="N34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="55" t="n">
-        <v>0.02</v>
+        <v>3</v>
+      </c>
+      <c r="O34" s="16" t="n">
+        <v>10</v>
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q34" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" s="60" t="inlineStr">
+      <c r="Q34" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="R34" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S34" s="8" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -5658,25 +5738,25 @@
         </is>
       </c>
       <c r="N35" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="O35" s="57" t="n">
-        <v>32.32</v>
+        <v>10</v>
+      </c>
+      <c r="O35" s="61" t="n">
+        <v>36.32</v>
       </c>
       <c r="P35" s="11" t="n">
         <v>78</v>
       </c>
-      <c r="Q35" s="57" t="n">
+      <c r="Q35" s="61" t="n">
         <v>78</v>
       </c>
-      <c r="R35" s="58" t="inlineStr">
+      <c r="R35" s="62" t="inlineStr">
         <is>
           <t>پرریسک</t>
         </is>
       </c>
       <c r="S35" s="12" t="inlineStr">
         <is>
-          <t>توقف افزایش اعتبار، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
+          <t>مسدودسازی سقف تسهیلات، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
         </is>
       </c>
     </row>
@@ -5733,7 +5813,7 @@
       <c r="N36" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O36" s="55" t="n">
+      <c r="O36" s="16" t="n">
         <v>0.2</v>
       </c>
       <c r="P36" s="7" t="inlineStr">
@@ -5741,17 +5821,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q36" s="55" t="n">
+      <c r="Q36" s="16" t="n">
         <v>0.2</v>
       </c>
-      <c r="R36" s="60" t="inlineStr">
+      <c r="R36" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S36" s="8" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5888,7 @@
       <c r="N37" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="O37" s="57" t="n">
+      <c r="O37" s="61" t="n">
         <v>1.14</v>
       </c>
       <c r="P37" s="11" t="inlineStr">
@@ -5816,17 +5896,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q37" s="57" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="R37" s="60" t="inlineStr">
+      <c r="Q37" s="61" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R37" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S37" s="12" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5963,7 @@
       <c r="N38" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O38" s="55" t="n">
+      <c r="O38" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="7" t="inlineStr">
@@ -5891,17 +5971,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q38" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" s="60" t="inlineStr">
+      <c r="Q38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S38" s="8" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -5956,25 +6036,25 @@
         </is>
       </c>
       <c r="N39" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="O39" s="57" t="n">
-        <v>55.38</v>
+        <v>10</v>
+      </c>
+      <c r="O39" s="61" t="n">
+        <v>61.38</v>
       </c>
       <c r="P39" s="11" t="n">
         <v>78</v>
       </c>
-      <c r="Q39" s="57" t="n">
+      <c r="Q39" s="61" t="n">
         <v>78</v>
       </c>
-      <c r="R39" s="58" t="inlineStr">
+      <c r="R39" s="62" t="inlineStr">
         <is>
           <t>پرریسک</t>
         </is>
       </c>
       <c r="S39" s="12" t="inlineStr">
         <is>
-          <t>توقف افزایش اعتبار، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
+          <t>مسدودسازی سقف تسهیلات، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6111,7 @@
       <c r="N40" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O40" s="55" t="n">
+      <c r="O40" s="16" t="n">
         <v>2.21</v>
       </c>
       <c r="P40" s="7" t="inlineStr">
@@ -6039,17 +6119,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q40" s="55" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R40" s="60" t="inlineStr">
+      <c r="Q40" s="16" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="R40" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S40" s="8" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6186,7 @@
       <c r="N41" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="O41" s="57" t="n">
+      <c r="O41" s="61" t="n">
         <v>0</v>
       </c>
       <c r="P41" s="11" t="inlineStr">
@@ -6114,17 +6194,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q41" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" s="60" t="inlineStr">
+      <c r="Q41" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S41" s="12" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6261,7 @@
       <c r="N42" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O42" s="55" t="n">
+      <c r="O42" s="16" t="n">
         <v>0.1</v>
       </c>
       <c r="P42" s="7" t="inlineStr">
@@ -6189,17 +6269,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q42" s="55" t="n">
+      <c r="Q42" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="R42" s="60" t="inlineStr">
+      <c r="R42" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S42" s="8" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -6254,25 +6334,25 @@
         </is>
       </c>
       <c r="N43" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="O43" s="57" t="n">
-        <v>20.96</v>
+        <v>8</v>
+      </c>
+      <c r="O43" s="61" t="n">
+        <v>16.96</v>
       </c>
       <c r="P43" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="Q43" s="57" t="n">
+      <c r="Q43" s="61" t="n">
         <v>45</v>
       </c>
-      <c r="R43" s="59" t="inlineStr">
+      <c r="R43" s="63" t="inlineStr">
         <is>
           <t>مراقبت</t>
         </is>
       </c>
       <c r="S43" s="12" t="inlineStr">
         <is>
-          <t>پایش هفتگی، اخذ تضمین مضاعف، عدم پذیرش چک جدید با سررسید بالای ۳۰ روز.</t>
+          <t>مسدودسازی سقف تسهیلات، اخذ تضمین مضاعف و پایش مستمر.</t>
         </is>
       </c>
     </row>
@@ -6329,23 +6409,23 @@
       <c r="N44" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="O44" s="55" t="n">
+      <c r="O44" s="16" t="n">
         <v>26.43</v>
       </c>
       <c r="P44" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="Q44" s="55" t="n">
+      <c r="Q44" s="16" t="n">
         <v>72</v>
       </c>
-      <c r="R44" s="58" t="inlineStr">
+      <c r="R44" s="62" t="inlineStr">
         <is>
           <t>پرریسک</t>
         </is>
       </c>
       <c r="S44" s="8" t="inlineStr">
         <is>
-          <t>توقف افزایش اعتبار، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
+          <t>مسدودسازی سقف تسهیلات، اخذ وثیقه ملکی/نقدی، پایش فشرده و کاهش تعهدات.</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6482,7 @@
       <c r="N45" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="O45" s="57" t="n">
+      <c r="O45" s="61" t="n">
         <v>0.03</v>
       </c>
       <c r="P45" s="11" t="inlineStr">
@@ -6410,17 +6490,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q45" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" s="60" t="inlineStr">
+      <c r="Q45" s="61" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="R45" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S45" s="12" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -6477,7 +6557,7 @@
       <c r="N46" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O46" s="55" t="n">
+      <c r="O46" s="16" t="n">
         <v>0.09</v>
       </c>
       <c r="P46" s="7" t="inlineStr">
@@ -6485,17 +6565,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q46" s="55" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="R46" s="60" t="inlineStr">
+      <c r="Q46" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R46" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S46" s="8" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -6552,7 +6632,7 @@
       <c r="N47" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="O47" s="57" t="n">
+      <c r="O47" s="61" t="n">
         <v>0.01</v>
       </c>
       <c r="P47" s="11" t="inlineStr">
@@ -6560,17 +6640,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q47" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" s="60" t="inlineStr">
+      <c r="Q47" s="61" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R47" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S47" s="12" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6707,7 @@
       <c r="N48" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O48" s="55" t="n">
+      <c r="O48" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P48" s="7" t="inlineStr">
@@ -6635,17 +6715,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q48" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="60" t="inlineStr">
+      <c r="Q48" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S48" s="8" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6782,7 @@
       <c r="N49" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="O49" s="57" t="n">
+      <c r="O49" s="61" t="n">
         <v>0</v>
       </c>
       <c r="P49" s="11" t="inlineStr">
@@ -6710,69 +6790,69 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q49" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" s="60" t="inlineStr">
+      <c r="Q49" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="64" t="inlineStr">
         <is>
           <t>کم‌ریسک</t>
         </is>
       </c>
       <c r="S49" s="12" t="inlineStr">
         <is>
-          <t>ادامه تعامل در سقف مصوب.</t>
+          <t>پذیرش چک روال عادی و ادامه تعامل در سقف مصوب.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="61" t="inlineStr">
+      <c r="A50" s="55" t="inlineStr">
         <is>
           <t>مجموع کل</t>
         </is>
       </c>
-      <c r="B50" s="62" t="n"/>
-      <c r="C50" s="62" t="n"/>
-      <c r="D50" s="62" t="n"/>
-      <c r="E50" s="62" t="n"/>
-      <c r="F50" s="62" t="n"/>
-      <c r="G50" s="63">
+      <c r="B50" s="56" t="n"/>
+      <c r="C50" s="56" t="n"/>
+      <c r="D50" s="56" t="n"/>
+      <c r="E50" s="56" t="n"/>
+      <c r="F50" s="56" t="n"/>
+      <c r="G50" s="46">
         <f>SUM(G4:G49)</f>
         <v/>
       </c>
-      <c r="H50" s="63">
+      <c r="H50" s="46">
         <f>SUM(H4:H49)</f>
         <v/>
       </c>
-      <c r="I50" s="64">
+      <c r="I50" s="47">
         <f>SUM(I4:I49)</f>
         <v/>
       </c>
-      <c r="J50" s="63">
+      <c r="J50" s="46">
         <f>SUM(J4:J49)</f>
         <v/>
       </c>
-      <c r="K50" s="63">
+      <c r="K50" s="46">
         <f>SUM(K4:K49)</f>
         <v/>
       </c>
-      <c r="L50" s="63">
+      <c r="L50" s="46">
         <f>SUM(L4:L49)</f>
         <v/>
       </c>
-      <c r="M50" s="62" t="n"/>
-      <c r="N50" s="62" t="n"/>
-      <c r="O50" s="62" t="n"/>
-      <c r="P50" s="62" t="n"/>
-      <c r="Q50" s="65">
+      <c r="M50" s="56" t="n"/>
+      <c r="N50" s="56" t="n"/>
+      <c r="O50" s="56" t="n"/>
+      <c r="P50" s="56" t="n"/>
+      <c r="Q50" s="58">
         <f>AVERAGE(Q4:Q49)</f>
         <v/>
       </c>
-      <c r="R50" s="66" t="inlineStr">
+      <c r="R50" s="45" t="inlineStr">
         <is>
           <t>میانگین سبد</t>
         </is>
       </c>
-      <c r="S50" s="62" t="n"/>
+      <c r="S50" s="56" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6909,7 +6989,7 @@
           <t>0941987231</t>
         </is>
       </c>
-      <c r="D4" s="67" t="inlineStr">
+      <c r="D4" s="65" t="inlineStr">
         <is>
           <t>انتقال تعهد در راه به برگشتی</t>
         </is>
@@ -6965,7 +7045,7 @@
           <t>0890543331</t>
         </is>
       </c>
-      <c r="D5" s="68" t="inlineStr">
+      <c r="D5" s="66" t="inlineStr">
         <is>
           <t>انتقال تعهد در راه به برگشتی</t>
         </is>
@@ -7021,7 +7101,7 @@
           <t>1920394974</t>
         </is>
       </c>
-      <c r="D6" s="67" t="inlineStr">
+      <c r="D6" s="65" t="inlineStr">
         <is>
           <t>انتقال تعهد در راه به برگشتی</t>
         </is>
@@ -7077,7 +7157,7 @@
           <t>0927624011</t>
         </is>
       </c>
-      <c r="D7" s="68" t="inlineStr">
+      <c r="D7" s="66" t="inlineStr">
         <is>
           <t>انتقال تعهد در راه به برگشتی</t>
         </is>
@@ -7133,7 +7213,7 @@
           <t>6510002647</t>
         </is>
       </c>
-      <c r="D8" s="67" t="inlineStr">
+      <c r="D8" s="65" t="inlineStr">
         <is>
           <t>انتقال تعهد در راه به برگشتی</t>
         </is>
@@ -7189,7 +7269,7 @@
           <t>0860270361</t>
         </is>
       </c>
-      <c r="D9" s="68" t="inlineStr">
+      <c r="D9" s="66" t="inlineStr">
         <is>
           <t>انتقال تعهد در راه به برگشتی</t>
         </is>
@@ -7245,7 +7325,7 @@
           <t>0941314121</t>
         </is>
       </c>
-      <c r="D10" s="69" t="inlineStr">
+      <c r="D10" s="67" t="inlineStr">
         <is>
           <t>رفع سوءاثر واقعی و تسویه برگشتی</t>
         </is>
@@ -7402,57 +7482,57 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="70" t="inlineStr">
+      <c r="A3" s="68" t="inlineStr">
         <is>
           <t>ردیف</t>
         </is>
       </c>
-      <c r="B3" s="70" t="inlineStr">
+      <c r="B3" s="68" t="inlineStr">
         <is>
           <t>نام صادرکننده</t>
         </is>
       </c>
-      <c r="C3" s="70" t="inlineStr">
+      <c r="C3" s="68" t="inlineStr">
         <is>
           <t>کد ملی صادرکننده</t>
         </is>
       </c>
-      <c r="D3" s="70" t="inlineStr">
+      <c r="D3" s="68" t="inlineStr">
         <is>
           <t>امتیاز ریسک</t>
         </is>
       </c>
-      <c r="E3" s="70" t="inlineStr">
+      <c r="E3" s="68" t="inlineStr">
         <is>
           <t>طبقه ریسک</t>
         </is>
       </c>
-      <c r="F3" s="70" t="inlineStr">
+      <c r="F3" s="68" t="inlineStr">
         <is>
           <t>مجموع تعهدات صندوق (ریال)</t>
         </is>
       </c>
-      <c r="G3" s="70" t="inlineStr">
+      <c r="G3" s="68" t="inlineStr">
         <is>
           <t>مبلغ برگشتی بانکی (ریال)</t>
         </is>
       </c>
-      <c r="H3" s="70" t="inlineStr">
+      <c r="H3" s="68" t="inlineStr">
         <is>
           <t>مبلغ در راه بانکی (ریال)</t>
         </is>
       </c>
-      <c r="I3" s="70" t="inlineStr">
+      <c r="I3" s="68" t="inlineStr">
         <is>
           <t>سابقه دوره‌های برگشتی</t>
         </is>
       </c>
-      <c r="J3" s="70" t="inlineStr">
+      <c r="J3" s="68" t="inlineStr">
         <is>
           <t>علل اصلی ورود به رده بحرانی</t>
         </is>
       </c>
-      <c r="K3" s="70" t="inlineStr">
+      <c r="K3" s="68" t="inlineStr">
         <is>
           <t>اقدامات الزامی و پروتکل حقوقی</t>
         </is>
@@ -7462,17 +7542,17 @@
       <c r="A4" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>حسین حشمتی</t>
         </is>
       </c>
-      <c r="C4" s="71" t="inlineStr">
+      <c r="C4" s="69" t="inlineStr">
         <is>
           <t>0933387075</t>
         </is>
       </c>
-      <c r="D4" s="72" t="n">
+      <c r="D4" s="70" t="n">
         <v>85</v>
       </c>
       <c r="E4" s="21" t="inlineStr">
@@ -7480,26 +7560,26 @@
           <t>اقدام فوری</t>
         </is>
       </c>
-      <c r="F4" s="24" t="n">
+      <c r="F4" s="22" t="n">
         <v>1060000000</v>
       </c>
-      <c r="G4" s="24" t="n">
+      <c r="G4" s="22" t="n">
         <v>56960000000</v>
       </c>
-      <c r="H4" s="24" t="n">
+      <c r="H4" s="22" t="n">
         <v>2500000000</v>
       </c>
       <c r="I4" s="21" t="inlineStr">
         <is>
-          <t>8 دوره (برگشتی مزمن)</t>
-        </is>
-      </c>
-      <c r="J4" s="25" t="inlineStr">
+          <t>2 دوره (برگشتی مزمن)</t>
+        </is>
+      </c>
+      <c r="J4" s="24" t="inlineStr">
         <is>
           <t>مبلغ برگشتی بالای ۵۰ میلیارد ریال (مشروط به کف اجباری ۸۵) و سابقه مزمن عدم تسویه</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="24" t="inlineStr">
         <is>
           <t>انسداد فوری حساب صندوق، ضبط و واخواست چک‌های نزد صندوق، ارسال اظهارنامه رسمی قضایی</t>
         </is>
@@ -7552,247 +7632,247 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="73" t="inlineStr">
+      <c r="A3" s="71" t="inlineStr">
         <is>
           <t>ردیف</t>
         </is>
       </c>
-      <c r="B3" s="73" t="inlineStr">
+      <c r="B3" s="71" t="inlineStr">
         <is>
           <t>نام صادرکننده</t>
         </is>
       </c>
-      <c r="C3" s="73" t="inlineStr">
+      <c r="C3" s="71" t="inlineStr">
         <is>
           <t>کد ملی صادرکننده</t>
         </is>
       </c>
-      <c r="D3" s="73" t="inlineStr">
+      <c r="D3" s="71" t="inlineStr">
         <is>
           <t>امتیاز ریسک</t>
         </is>
       </c>
-      <c r="E3" s="73" t="inlineStr">
+      <c r="E3" s="71" t="inlineStr">
         <is>
           <t>رده ریسک</t>
         </is>
       </c>
-      <c r="F3" s="73" t="inlineStr">
+      <c r="F3" s="71" t="inlineStr">
         <is>
           <t>تعهدات صندوق (ریال)</t>
         </is>
       </c>
-      <c r="G3" s="73" t="inlineStr">
+      <c r="G3" s="71" t="inlineStr">
         <is>
           <t>مبلغ برگشتی بانکی (ریال)</t>
         </is>
       </c>
-      <c r="H3" s="73" t="inlineStr">
+      <c r="H3" s="71" t="inlineStr">
         <is>
           <t>مبلغ در راه بانکی (ریال)</t>
         </is>
       </c>
-      <c r="I3" s="73" t="inlineStr">
+      <c r="I3" s="71" t="inlineStr">
         <is>
           <t>سابقه دوره‌های برگشتی</t>
         </is>
       </c>
-      <c r="J3" s="73" t="inlineStr">
+      <c r="J3" s="71" t="inlineStr">
         <is>
           <t>علل قرارگیری در مراقبت</t>
         </is>
       </c>
-      <c r="K3" s="73" t="inlineStr">
+      <c r="K3" s="71" t="inlineStr">
         <is>
           <t>اقدامات پیشگیرانه و مراقبتی</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="33" t="n">
+      <c r="A4" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>وحید محمدی انور</t>
         </is>
       </c>
-      <c r="C4" s="74" t="inlineStr">
+      <c r="C4" s="72" t="inlineStr">
         <is>
           <t>1920394974</t>
         </is>
       </c>
-      <c r="D4" s="75" t="n">
+      <c r="D4" s="73" t="n">
+        <v>52.93</v>
+      </c>
+      <c r="E4" s="31" t="inlineStr">
+        <is>
+          <t>مراقبت</t>
+        </is>
+      </c>
+      <c r="F4" s="32" t="n">
+        <v>7400000000</v>
+      </c>
+      <c r="G4" s="32" t="n">
+        <v>4200000000</v>
+      </c>
+      <c r="H4" s="32" t="n">
+        <v>12989000000</v>
+      </c>
+      <c r="I4" s="31" t="inlineStr">
+        <is>
+          <t>10 دوره</t>
+        </is>
+      </c>
+      <c r="J4" s="34" t="inlineStr">
+        <is>
+          <t>برگشتی فعال ۴.۲ میلیارد ریالی و سابقه ۱۰ دوره برگشتی در استعلام‌های تاریخی</t>
+        </is>
+      </c>
+      <c r="K4" s="34" t="inlineStr">
+        <is>
+          <t>اخذ تضمین فرعی، پایش روزانه، عدم افزایش اعتبار و نظارت مستمر بر مبالغ در راه</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="34" t="inlineStr">
+        <is>
+          <t>سیدجمال موسوی علی آبادی</t>
+        </is>
+      </c>
+      <c r="C5" s="72" t="inlineStr">
+        <is>
+          <t>6510002647</t>
+        </is>
+      </c>
+      <c r="D5" s="73" t="n">
         <v>45</v>
       </c>
-      <c r="E4" s="33" t="inlineStr">
+      <c r="E5" s="31" t="inlineStr">
         <is>
           <t>مراقبت</t>
         </is>
       </c>
-      <c r="F4" s="36" t="n">
-        <v>7400000000</v>
-      </c>
-      <c r="G4" s="36" t="n">
-        <v>4200000000</v>
-      </c>
-      <c r="H4" s="36" t="n">
-        <v>12989000000</v>
-      </c>
-      <c r="I4" s="33" t="inlineStr">
+      <c r="F5" s="32" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="G5" s="32" t="n">
+        <v>2800000000</v>
+      </c>
+      <c r="H5" s="32" t="n">
+        <v>35090000000</v>
+      </c>
+      <c r="I5" s="31" t="inlineStr">
+        <is>
+          <t>6 دوره</t>
+        </is>
+      </c>
+      <c r="J5" s="34" t="inlineStr">
+        <is>
+          <t>برگشتی فعال ۱.۵ میلیارد ریالی، انتقال تعهد در راه به برگشتی و سابقه ۶ دوره برگشتی</t>
+        </is>
+      </c>
+      <c r="K5" s="34" t="inlineStr">
+        <is>
+          <t>پایش روزانه، کنترل وصولی‌ها و عدم پذیرش چک جدید بدون وثیقه نقد</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>میلاد دلجو</t>
+        </is>
+      </c>
+      <c r="C6" s="72" t="inlineStr">
+        <is>
+          <t>2710183331</t>
+        </is>
+      </c>
+      <c r="D6" s="73" t="n">
+        <v>45</v>
+      </c>
+      <c r="E6" s="31" t="inlineStr">
+        <is>
+          <t>مراقبت</t>
+        </is>
+      </c>
+      <c r="F6" s="32" t="n">
+        <v>27500000000</v>
+      </c>
+      <c r="G6" s="32" t="n">
+        <v>1326000000</v>
+      </c>
+      <c r="H6" s="32" t="n">
+        <v>93388000000</v>
+      </c>
+      <c r="I6" s="31" t="inlineStr">
         <is>
           <t>8 دوره</t>
         </is>
       </c>
-      <c r="J4" s="37" t="inlineStr">
-        <is>
-          <t>نوسان در چک‌های در راه، سابقه برگشتی مثبت یا ریسک تمرکز تعهدات نزد صندوق</t>
-        </is>
-      </c>
-      <c r="K4" s="37" t="inlineStr">
-        <is>
-          <t>اخذ چک تضمین شخص ثالث، تماس ۷۲ ساعت قبل از سررسید، محدودسازی صدور چک جدید</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="37" t="inlineStr">
-        <is>
-          <t>سیدجمال موسوی علی آبادی</t>
-        </is>
-      </c>
-      <c r="C5" s="74" t="inlineStr">
-        <is>
-          <t>6510002647</t>
-        </is>
-      </c>
-      <c r="D5" s="75" t="n">
+      <c r="J6" s="34" t="inlineStr">
+        <is>
+          <t>ریسک تمرکز بالای تعهدات نزد صندوق (۲۷.۵ میلیارد ریال) و برگشتی فعال ۱.۳۲۶ میلیارد ریالی</t>
+        </is>
+      </c>
+      <c r="K6" s="34" t="inlineStr">
+        <is>
+          <t>اخذ تضمین فرعی، کنترل استعلام‌های آتی، پایش هفتگی و عدم افزایش تعهدات</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>جواد غفوریان قالی باف</t>
+        </is>
+      </c>
+      <c r="C7" s="72" t="inlineStr">
+        <is>
+          <t>0941314121</t>
+        </is>
+      </c>
+      <c r="D7" s="73" t="n">
         <v>45</v>
       </c>
-      <c r="E5" s="33" t="inlineStr">
+      <c r="E7" s="31" t="inlineStr">
         <is>
           <t>مراقبت</t>
         </is>
       </c>
-      <c r="F5" s="36" t="n">
-        <v>3000000000</v>
-      </c>
-      <c r="G5" s="36" t="n">
-        <v>2800000000</v>
-      </c>
-      <c r="H5" s="36" t="n">
-        <v>35090000000</v>
-      </c>
-      <c r="I5" s="33" t="inlineStr">
-        <is>
-          <t>5 دوره</t>
-        </is>
-      </c>
-      <c r="J5" s="37" t="inlineStr">
-        <is>
-          <t>نوسان در چک‌های در راه، سابقه برگشتی مثبت یا ریسک تمرکز تعهدات نزد صندوق</t>
-        </is>
-      </c>
-      <c r="K5" s="37" t="inlineStr">
-        <is>
-          <t>اخذ چک تضمین شخص ثالث، تماس ۷۲ ساعت قبل از سررسید، محدودسازی صدور چک جدید</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="37" t="inlineStr">
-        <is>
-          <t>میلاد دلجو</t>
-        </is>
-      </c>
-      <c r="C6" s="74" t="inlineStr">
-        <is>
-          <t>2710183331</t>
-        </is>
-      </c>
-      <c r="D6" s="75" t="n">
-        <v>45</v>
-      </c>
-      <c r="E6" s="33" t="inlineStr">
-        <is>
-          <t>مراقبت</t>
-        </is>
-      </c>
-      <c r="F6" s="36" t="n">
-        <v>27500000000</v>
-      </c>
-      <c r="G6" s="36" t="n">
-        <v>1326000000</v>
-      </c>
-      <c r="H6" s="36" t="n">
-        <v>93388000000</v>
-      </c>
-      <c r="I6" s="33" t="inlineStr">
-        <is>
-          <t>10 دوره</t>
-        </is>
-      </c>
-      <c r="J6" s="37" t="inlineStr">
-        <is>
-          <t>نوسان در چک‌های در راه، سابقه برگشتی مثبت یا ریسک تمرکز تعهدات نزد صندوق</t>
-        </is>
-      </c>
-      <c r="K6" s="37" t="inlineStr">
-        <is>
-          <t>اخذ چک تضمین شخص ثالث، تماس ۷۲ ساعت قبل از سررسید، محدودسازی صدور چک جدید</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="37" t="inlineStr">
-        <is>
-          <t>جواد غفوریان قالی باف</t>
-        </is>
-      </c>
-      <c r="C7" s="74" t="inlineStr">
-        <is>
-          <t>0941314121</t>
-        </is>
-      </c>
-      <c r="D7" s="75" t="n">
-        <v>45</v>
-      </c>
-      <c r="E7" s="33" t="inlineStr">
-        <is>
-          <t>مراقبت</t>
-        </is>
-      </c>
-      <c r="F7" s="36" t="n">
+      <c r="F7" s="32" t="n">
         <v>7000000000</v>
       </c>
-      <c r="G7" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="36" t="n">
+      <c r="G7" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="32" t="n">
         <v>28682000000</v>
       </c>
-      <c r="I7" s="33" t="inlineStr">
-        <is>
-          <t>1 دوره</t>
-        </is>
-      </c>
-      <c r="J7" s="37" t="inlineStr">
-        <is>
-          <t>نوسان در چک‌های در راه، سابقه برگشتی مثبت یا ریسک تمرکز تعهدات نزد صندوق</t>
-        </is>
-      </c>
-      <c r="K7" s="37" t="inlineStr">
-        <is>
-          <t>اخذ چک تضمین شخص ثالث، تماس ۷۲ ساعت قبل از سررسید، محدودسازی صدور چک جدید</t>
+      <c r="I7" s="31" t="inlineStr">
+        <is>
+          <t>3 دوره</t>
+        </is>
+      </c>
+      <c r="J7" s="34" t="inlineStr">
+        <is>
+          <t>دوره گذار پایش پس از تسویه ۱ میلیارد ریال چک برگشتی؛ اعمال کف ۴۵ مراقبت</t>
+        </is>
+      </c>
+      <c r="K7" s="34" t="inlineStr">
+        <is>
+          <t>پایش روزانه، کنترل چک‌های در راه، عدم افزایش سقف اعتباری (دوره گذار پایش پس از تسویه)</t>
         </is>
       </c>
     </row>
@@ -7823,7 +7903,7 @@
     <col width="27" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
     <col width="65" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
@@ -7843,134 +7923,134 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="76" t="inlineStr">
+      <c r="A3" s="74" t="inlineStr">
         <is>
           <t>ردیف</t>
         </is>
       </c>
-      <c r="B3" s="76" t="inlineStr">
+      <c r="B3" s="74" t="inlineStr">
         <is>
           <t>نام صادرکننده</t>
         </is>
       </c>
-      <c r="C3" s="76" t="inlineStr">
+      <c r="C3" s="74" t="inlineStr">
         <is>
           <t>کد ملی صادرکننده</t>
         </is>
       </c>
-      <c r="D3" s="76" t="inlineStr">
+      <c r="D3" s="74" t="inlineStr">
         <is>
           <t>مبلغ رفع سوءاثر جدید (ریال)</t>
         </is>
       </c>
-      <c r="E3" s="76" t="inlineStr">
+      <c r="E3" s="74" t="inlineStr">
         <is>
           <t>کاهش در مبلغ برگشتی (ریال)</t>
         </is>
       </c>
-      <c r="F3" s="76" t="inlineStr">
+      <c r="F3" s="74" t="inlineStr">
         <is>
           <t>مبلغ فعلی برگشتی (ریال)</t>
         </is>
       </c>
-      <c r="G3" s="76" t="inlineStr">
+      <c r="G3" s="74" t="inlineStr">
         <is>
           <t>مبلغ در راه بانکی (ریال)</t>
         </is>
       </c>
-      <c r="H3" s="76" t="inlineStr">
+      <c r="H3" s="74" t="inlineStr">
         <is>
           <t>امتیاز فعلی ریسک</t>
         </is>
       </c>
-      <c r="I3" s="76" t="inlineStr">
+      <c r="I3" s="74" t="inlineStr">
         <is>
           <t>وضعیت اعتباری سامانه</t>
         </is>
       </c>
-      <c r="J3" s="76" t="inlineStr">
+      <c r="J3" s="74" t="inlineStr">
         <is>
           <t>مجوز تمدید و ارزیابی</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="44" t="n">
+      <c r="A4" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="48" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>جواد غفوریان قالی باف</t>
         </is>
       </c>
-      <c r="C4" s="77" t="inlineStr">
+      <c r="C4" s="72" t="inlineStr">
         <is>
           <t>0941314121</t>
         </is>
       </c>
-      <c r="D4" s="47" t="n">
+      <c r="D4" s="32" t="n">
         <v>1000000000</v>
       </c>
-      <c r="E4" s="47" t="n">
+      <c r="E4" s="32" t="n">
         <v>1000000000</v>
       </c>
-      <c r="F4" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="47" t="n">
+      <c r="F4" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="32" t="n">
         <v>28682000000</v>
       </c>
-      <c r="H4" s="78" t="n">
+      <c r="H4" s="73" t="n">
         <v>45</v>
       </c>
-      <c r="I4" s="44" t="inlineStr">
-        <is>
-          <t>روند ترمیمی / خوش‌حساب</t>
-        </is>
-      </c>
-      <c r="J4" s="48" t="inlineStr">
-        <is>
-          <t>تسویه موفق چک‌های برگشتی گذشته؛ مجاز به بررسی ارتقای سقف اعتباری در صورت تداوم حسن حساب</t>
+      <c r="I4" s="63" t="inlineStr">
+        <is>
+          <t>دوره گذار پایش (مراقبت)</t>
+        </is>
+      </c>
+      <c r="J4" s="34" t="inlineStr">
+        <is>
+          <t>تسویه اخیر ۱ میلیارد ریال؛ دوره گذار پایش، پایش روزانه، تثبیت سقف و ممنوعیت ارتقای تعهدات</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="44" t="n">
+      <c r="A5" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="48" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>وحید اشرافیان</t>
         </is>
       </c>
-      <c r="C5" s="77" t="inlineStr">
+      <c r="C5" s="75" t="inlineStr">
         <is>
           <t>0921320711</t>
         </is>
       </c>
-      <c r="D5" s="47" t="n">
+      <c r="D5" s="27" t="n">
         <v>780000000</v>
       </c>
-      <c r="E5" s="47" t="n">
+      <c r="E5" s="27" t="n">
         <v>170000000</v>
       </c>
-      <c r="F5" s="47" t="n">
+      <c r="F5" s="27" t="n">
         <v>6247000000</v>
       </c>
-      <c r="G5" s="47" t="n">
+      <c r="G5" s="27" t="n">
         <v>263677279312</v>
       </c>
-      <c r="H5" s="78" t="n">
+      <c r="H5" s="76" t="n">
         <v>65</v>
       </c>
-      <c r="I5" s="44" t="inlineStr">
-        <is>
-          <t>روند ترمیمی / خوش‌حساب</t>
-        </is>
-      </c>
-      <c r="J5" s="48" t="inlineStr">
-        <is>
-          <t>تسویه موفق چک‌های برگشتی گذشته؛ مجاز به بررسی ارتقای سقف اعتباری در صورت تداوم حسن حساب</t>
+      <c r="I5" s="62" t="inlineStr">
+        <is>
+          <t>بهبود نسبی (پرریسک)</t>
+        </is>
+      </c>
+      <c r="J5" s="29" t="inlineStr">
+        <is>
+          <t>بهبود نسبی، پایش روزانه، تثبیت سقف تسهیلات، درخواست تضمین تکمیلی</t>
         </is>
       </c>
     </row>
@@ -20798,37 +20878,37 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="61" t="inlineStr">
+      <c r="A149" s="55" t="inlineStr">
         <is>
           <t>مجموع کل</t>
         </is>
       </c>
-      <c r="B149" s="62" t="n"/>
-      <c r="C149" s="62" t="n"/>
-      <c r="D149" s="62" t="n"/>
-      <c r="E149" s="62" t="n"/>
-      <c r="F149" s="62" t="n"/>
-      <c r="G149" s="62" t="n"/>
-      <c r="H149" s="62" t="n"/>
-      <c r="I149" s="62" t="n"/>
-      <c r="J149" s="62" t="n"/>
-      <c r="K149" s="62" t="n"/>
-      <c r="L149" s="63">
+      <c r="B149" s="56" t="n"/>
+      <c r="C149" s="56" t="n"/>
+      <c r="D149" s="56" t="n"/>
+      <c r="E149" s="56" t="n"/>
+      <c r="F149" s="56" t="n"/>
+      <c r="G149" s="56" t="n"/>
+      <c r="H149" s="56" t="n"/>
+      <c r="I149" s="56" t="n"/>
+      <c r="J149" s="56" t="n"/>
+      <c r="K149" s="56" t="n"/>
+      <c r="L149" s="46">
         <f>SUM(L2:L148)</f>
         <v/>
       </c>
-      <c r="M149" s="62" t="n"/>
-      <c r="N149" s="62" t="n"/>
-      <c r="O149" s="62" t="n"/>
-      <c r="P149" s="62" t="n"/>
-      <c r="Q149" s="62" t="n"/>
-      <c r="R149" s="62" t="n"/>
-      <c r="S149" s="62" t="n"/>
-      <c r="T149" s="62" t="n"/>
-      <c r="U149" s="62" t="n"/>
-      <c r="V149" s="62" t="n"/>
-      <c r="W149" s="62" t="n"/>
-      <c r="X149" s="62" t="n"/>
+      <c r="M149" s="56" t="n"/>
+      <c r="N149" s="56" t="n"/>
+      <c r="O149" s="56" t="n"/>
+      <c r="P149" s="56" t="n"/>
+      <c r="Q149" s="56" t="n"/>
+      <c r="R149" s="56" t="n"/>
+      <c r="S149" s="56" t="n"/>
+      <c r="T149" s="56" t="n"/>
+      <c r="U149" s="56" t="n"/>
+      <c r="V149" s="56" t="n"/>
+      <c r="W149" s="56" t="n"/>
+      <c r="X149" s="56" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20842,17 +20922,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
-    <col width="59" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="65" customWidth="1" min="8" max="8"/>
     <col width="65" customWidth="1" min="9" max="9"/>
     <col width="62" customWidth="1" min="10" max="10"/>
   </cols>
@@ -21061,7 +21141,7 @@
           <t>مبلغ برگشتی بانکی صادرکننده</t>
         </is>
       </c>
-      <c r="B13" s="56" t="inlineStr">
+      <c r="B13" s="60" t="inlineStr">
         <is>
           <t>۵۶,۹۶۰,۰۰۰,۰۰۰ ریال (مشمول کف ۸۵)</t>
         </is>
@@ -21083,7 +21163,7 @@
           <t>طبقه ریسک اعتباری سامانه</t>
         </is>
       </c>
-      <c r="B14" s="56" t="inlineStr">
+      <c r="B14" s="60" t="inlineStr">
         <is>
           <t>اقدام فوری (امتیاز ۸۵.۰)</t>
         </is>
@@ -21207,26 +21287,26 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="61" t="inlineStr">
+      <c r="A20" s="55" t="inlineStr">
         <is>
           <t>مجموع</t>
         </is>
       </c>
-      <c r="B20" s="62" t="n"/>
-      <c r="C20" s="62" t="n"/>
-      <c r="D20" s="62" t="n"/>
-      <c r="E20" s="62" t="n"/>
-      <c r="F20" s="62" t="n"/>
-      <c r="G20" s="62" t="n"/>
-      <c r="H20" s="63" t="n">
+      <c r="B20" s="56" t="n"/>
+      <c r="C20" s="56" t="n"/>
+      <c r="D20" s="56" t="n"/>
+      <c r="E20" s="56" t="n"/>
+      <c r="F20" s="56" t="n"/>
+      <c r="G20" s="56" t="n"/>
+      <c r="H20" s="46" t="n">
         <v>220000000</v>
       </c>
-      <c r="I20" s="79" t="inlineStr">
+      <c r="I20" s="59" t="inlineStr">
         <is>
           <t>مجموع اسناد با هویت حل‌نشده</t>
         </is>
       </c>
-      <c r="J20" s="62" t="n"/>
+      <c r="J20" s="56" t="n"/>
     </row>
     <row r="21"/>
     <row r="22"/>
@@ -21382,56 +21462,486 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="61" t="inlineStr">
+      <c r="A27" s="55" t="inlineStr">
         <is>
           <t>مجموع</t>
         </is>
       </c>
-      <c r="B27" s="62" t="n"/>
-      <c r="C27" s="62" t="n"/>
-      <c r="D27" s="62" t="n"/>
-      <c r="E27" s="62" t="n"/>
-      <c r="F27" s="62" t="n"/>
-      <c r="G27" s="62" t="n"/>
-      <c r="H27" s="63" t="n">
+      <c r="B27" s="56" t="n"/>
+      <c r="C27" s="56" t="n"/>
+      <c r="D27" s="56" t="n"/>
+      <c r="E27" s="56" t="n"/>
+      <c r="F27" s="56" t="n"/>
+      <c r="G27" s="56" t="n"/>
+      <c r="H27" s="46" t="n">
         <v>3400000000</v>
       </c>
-      <c r="I27" s="79" t="inlineStr">
+      <c r="I27" s="59" t="inlineStr">
         <is>
           <t>مجموع اسناد معاف از استعلام صیاد</t>
         </is>
       </c>
-      <c r="J27" s="62" t="n"/>
+      <c r="J27" s="56" t="n"/>
     </row>
     <row r="28"/>
     <row r="29">
-      <c r="A29" s="80" t="inlineStr">
+      <c r="A29" s="77" t="inlineStr">
         <is>
           <t>مجموع کل تفکیکی</t>
         </is>
       </c>
-      <c r="B29" s="62" t="n"/>
-      <c r="C29" s="62" t="n"/>
-      <c r="D29" s="62" t="n"/>
-      <c r="E29" s="62" t="n"/>
-      <c r="F29" s="62" t="n"/>
-      <c r="G29" s="62" t="n"/>
-      <c r="H29" s="63" t="n">
+      <c r="B29" s="56" t="n"/>
+      <c r="C29" s="56" t="n"/>
+      <c r="D29" s="56" t="n"/>
+      <c r="E29" s="56" t="n"/>
+      <c r="F29" s="56" t="n"/>
+      <c r="G29" s="56" t="n"/>
+      <c r="H29" s="46" t="n">
         <v>3620000000</v>
       </c>
-      <c r="I29" s="79" t="inlineStr">
+      <c r="I29" s="59" t="inlineStr">
         <is>
           <t>تفاضل تعهدات صندوق با پروفایل‌های معتبر (۴۸۳.۳۲۵B - ۴۷۹.۷۰۵B)</t>
         </is>
       </c>
-      <c r="J29" s="62" t="n"/>
+      <c r="J29" s="56" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>۴. جدول تفکیک قطعی و رفع تعارض دو فقره چک ۱.۴ میلیارد ریالی احمد زحمتکش (چک معاف ۶۶۶۶۶ در برابر چک صیادی ۱۷۹۶۸۷)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>مشخصه کنترلی سند</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>سند ۱: چک تمدید معاف از استعلام صیادی (شیت ۰۸)</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t>سند ۲: چک صیادی بانکی معتبر نزد صندوق (شیت ۰۲ و ۰۷)</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>ارزیابی ممیزی و عدم جابه‌جایی سریال‌ها</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>شماره سریال در سیستم حسابداری</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>66666 (ثبت دستی)</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>179687 (سری صیاد ۲۶۴۰)</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>سریال‌های کاملاً مستقل و متمایز در دفاتر صندوق</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>شناسه ۱۶ رقمی صیاد</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>فاقد شناسه صیاد (سند تمدیدی/معاف)</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>5783030115225521</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>چک ۱۷۹۶۸۷ استعلام سیستمی شده و دارای سابقه صیادی است</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>شرح سند در دفاتر مالی</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>چک تمدید احمد زحمتکش</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>چک صیادی قرارداد فروش</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>شرح و منشأ حسابداری دو سند کاملاً مجزاست</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>مبلغ ریالی سند</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>۱,۴۰۰,۰۰۰,۰۰۰ ریال</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>۱,۴۰۰,۰۰۰,۰۰۰ ریال</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>مبالغ مساوی اما اسناد فیزیکی مستقل هستند</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>نام بانک و شعبه</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>بانک ملی کوی المهدی</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>بانک ملی کوی المهدی (کد ۲۶۴۰)</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>حساب‌های جاری صادرکننده در همان شعبه</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>وضعیت در محاسبات اعتباری</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>معاف از استعلام صیادی (EXEMPT)</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>چک معتبر بانکی دارای استعلام (VALID)</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>چک صیادی در پروفایل بانکی زحمتکش منظور شده است</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>جایگاه در ممیزی سبد</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>جزو ۳.۶۲۰ میلیارد ریال اسناد تفکیکی خارج از پروفایل</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>جزو ۴.۲ میلیارد ریال (۳ فقره چک) زحمتکش در شیت ۰۲</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>چک‌های صیادی زحمتکش: ۱۷۹۶۸۶ + ۱۷۹۶۸۷ + ۱۷۹۶۸۸ = ۴.۲B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>شمول در جمع ۴۷۹.۷۰۵B معتبر</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>خیر (مستثنی در شیت ۰۸)</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>بله (منظور در جمع ۴۷۹.۷۰۵B صندوق)</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>تطابق کامل با ارقام مرجع و عدم دوباره‌شماری یا جابه‌جایی</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>۵. جدول تفکیک قطعی مغایرت ۳.۶۲۰ میلیارد ریال صندوق (کل اسناد ۴۸۳.۳۲۵B در برابر معتبر ۴۷۹.۷۰۵B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>ردیف</t>
+        </is>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>کد مشتری</t>
+        </is>
+      </c>
+      <c r="C44" s="19" t="inlineStr">
+        <is>
+          <t>نام صادرکننده / متعهد</t>
+        </is>
+      </c>
+      <c r="D44" s="19" t="inlineStr">
+        <is>
+          <t>نوع سند در صندوق</t>
+        </is>
+      </c>
+      <c r="E44" s="19" t="inlineStr">
+        <is>
+          <t>شماره سریال سند</t>
+        </is>
+      </c>
+      <c r="F44" s="19" t="inlineStr">
+        <is>
+          <t>شناسه صیاد منشأ</t>
+        </is>
+      </c>
+      <c r="G44" s="19" t="inlineStr">
+        <is>
+          <t>مبلغ سند (ریال)</t>
+        </is>
+      </c>
+      <c r="H44" s="19" t="inlineStr">
+        <is>
+          <t>علت تفکیک از پروفایل معتبر</t>
+        </is>
+      </c>
+      <c r="I44" s="19" t="inlineStr">
+        <is>
+          <t>وضعیت در جمع ۴۷۹.۷۰۵B</t>
+        </is>
+      </c>
+      <c r="J44" s="19" t="inlineStr">
+        <is>
+          <t>مستند کنترلی ممیزی</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B45" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>امیرحسین علیپور</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>سفته حسن انجام تعهدات</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>1113333</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>فاقد شناسه صیاد</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>سند معاف از استعلام صیادی؛ تعهد مستقیم ضمانتی</t>
+        </is>
+      </c>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>خارج از پروفایل‌های صیادی</t>
+        </is>
+      </c>
+      <c r="J45" s="12" t="inlineStr">
+        <is>
+          <t>انطباق با بند R1 و AUD-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>احمد زحمتکش باجگیران</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>چک تمدید ضمانتی</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>66666</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>فاقد شناسه صیاد</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="n">
+        <v>1400000000</v>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>چک دستی تمدیدی بدون کد صیاد؛ معاف از استعلام صیاد</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>خارج از پروفایل‌های صیادی</t>
+        </is>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>انطباق با بند R1 و AUD-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B47" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>داوود رنگرززاده</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>چک بانکی فاقد کدملی</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>415569</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>چک ۳۲</t>
+        </is>
+      </c>
+      <c r="G47" s="14" t="n">
+        <v>220000000</v>
+      </c>
+      <c r="H47" s="12" t="inlineStr">
+        <is>
+          <t>هویت حل‌نشده به دلیل عدم ثبت کدملی در سیستم صندوق</t>
+        </is>
+      </c>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>خارج از پروفایل‌های صیادی</t>
+        </is>
+      </c>
+      <c r="J47" s="12" t="inlineStr">
+        <is>
+          <t>انطباق با بند R1 و AUD-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="77" t="inlineStr">
+        <is>
+          <t>مجموع مغایرت</t>
+        </is>
+      </c>
+      <c r="B48" s="56" t="n"/>
+      <c r="C48" s="56" t="n"/>
+      <c r="D48" s="56" t="n"/>
+      <c r="E48" s="56" t="n"/>
+      <c r="F48" s="56" t="n"/>
+      <c r="G48" s="46">
+        <f>SUM(G45:G47)</f>
+        <v/>
+      </c>
+      <c r="H48" s="59" t="inlineStr">
+        <is>
+          <t>دقیقاً برابر با ۳,۶۲۰,۰۰۰,۰۰۰ ریال تفاضل صندوق با پروفایل‌های معتبر</t>
+        </is>
+      </c>
+      <c r="I48" s="56" t="n"/>
+      <c r="J48" s="56" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A32:J32"/>
     <mergeCell ref="A17:J17"/>
     <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A43:J43"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21445,7 +21955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -21453,44 +21963,44 @@
     <col width="65" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
     <col width="65" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
     <col width="29" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="43" customWidth="1" min="9" max="9"/>
+    <col width="47" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>سیستم ممیزی دوگانه مستقل و اعتبارسنجی انطباق داده‌ها (Dual-Audit Engine)</t>
+          <t>سیستم ممیزی مستقل چندبعدی و اعتبارسنجی انطباق داده‌ها (Dual-Audit Engine)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="81" t="inlineStr">
-        <is>
-          <t>۱۴ آزمون کنترلی خودکار اکسل بر اساس معیارهای پذیرش کارفرما (Acceptance Criteria 1 to 4) | خروجی فرمولی خودکار: PASS / FAIL</t>
+      <c r="A2" s="78" t="inlineStr">
+        <is>
+          <t>۱۹ آزمون کنترلی خودکار اکسل بر اساس معیارهای نظارتی، رفتاری و هویتی ۱۴۰۵/۰۶/۱۵ | خروجی فرمولی خودکار: PASS / FAIL</t>
         </is>
       </c>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="82" t="inlineStr">
+      <c r="A4" s="79" t="inlineStr">
         <is>
           <t>وضعیت کل سیستم ممیزی:
-تایید کامل (PASS 14/14)</t>
-        </is>
-      </c>
-      <c r="C4" s="83" t="inlineStr">
-        <is>
-          <t>تعداد کل آزمون‌ها: ۱۴ آزمون
-آزمون‌های موفق: ۱۴ | آزمون‌های ردشده: ۰</t>
-        </is>
-      </c>
-      <c r="E4" s="84" t="inlineStr">
+تایید کامل (PASS 19/19)</t>
+        </is>
+      </c>
+      <c r="C4" s="80" t="inlineStr">
+        <is>
+          <t>تعداد کل آزمون‌ها: 19 آزمون
+آزمون‌های موفق: 19 | آزمون‌های ردشده: ۰</t>
+        </is>
+      </c>
+      <c r="E4" s="81" t="inlineStr">
         <is>
           <t>بیانیه الزامی ممیزی:
-«محاسبات بانکی بر اساس مشتری یکتا انجام شد و هیچ مبلغ در راه/برگشتی/رفع سوءاثر به دلیل تعدد چک دوباره‌شماری نشده است»</t>
+«ممیزی مشتری‌محور، هویتی، تاریخی و رفتاری انجام شد؛ 46 پروفایل معتبر، 13 مشتری دارای برگشتی فعال، Duplicate صفر، جمع برگشتی 244,751,000,000 ریال و تمام شاخص‌های Persistence بر اساس Snapshot یکتای هر مشتری/تاریخ محاسبه شده‌اند.»</t>
         </is>
       </c>
     </row>
@@ -21544,623 +22054,838 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="85" t="n">
+      <c r="A8" s="82" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="85" t="inlineStr">
+      <c r="B8" s="82" t="inlineStr">
         <is>
           <t>AUD-01</t>
         </is>
       </c>
-      <c r="C8" s="86" t="inlineStr">
+      <c r="C8" s="83" t="inlineStr">
         <is>
           <t>صحت تجمیع پروفایل‌های بانکی معتبر (عدم تکرار)</t>
         </is>
       </c>
-      <c r="D8" s="86" t="inlineStr">
+      <c r="D8" s="83" t="inlineStr">
         <is>
           <t>تعداد ردیف‌های مشتریان دارای پروفایل بانکی صیادی معتبر در جدول اصلی دقیقاً برابر با ۴۶ پروفایل یکتا است.</t>
         </is>
       </c>
-      <c r="E8" s="86" t="inlineStr">
+      <c r="E8" s="83" t="inlineStr">
         <is>
           <t>02_مشتریان_یکتا (B4:B49)</t>
         </is>
       </c>
-      <c r="F8" s="86" t="inlineStr">
+      <c r="F8" s="83" t="inlineStr">
         <is>
           <t>۴۶ پروفایل بانکی معتبر</t>
         </is>
       </c>
-      <c r="G8" s="87">
+      <c r="G8" s="84">
         <f>IF(COUNTA('02_مشتریان_یکتا'!B4:B49)=46, "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="H8" s="88">
+      <c r="H8" s="85">
         <f>IF(COUNTA('02_مشتریان_یکتا'!B4:B49)=46, "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="I8" s="85" t="inlineStr">
+      <c r="I8" s="82" t="inlineStr">
         <is>
           <t>AC 1 (Valid Canonical Profiles Count)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="89" t="n">
+      <c r="A9" s="86" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="89" t="inlineStr">
+      <c r="B9" s="86" t="inlineStr">
         <is>
           <t>AUD-02</t>
         </is>
       </c>
-      <c r="C9" s="90" t="inlineStr">
+      <c r="C9" s="87" t="inlineStr">
         <is>
           <t>یکتایی کدملی و عدم وجود Duplicate در پروفایل‌های معتبر</t>
         </is>
       </c>
-      <c r="D9" s="90" t="inlineStr">
+      <c r="D9" s="87" t="inlineStr">
         <is>
           <t>هر کدملی در میان ۴۶ پروفایل بانکی معتبر حداکثر یک بار تکرار شده و هیچ‌گونه هم‌پوشانی یا تکرار وجود ندارد.</t>
         </is>
       </c>
-      <c r="E9" s="90" t="inlineStr">
+      <c r="E9" s="87" t="inlineStr">
         <is>
           <t>02_مشتریان_یکتا (C4:C49)</t>
         </is>
       </c>
-      <c r="F9" s="90" t="inlineStr">
+      <c r="F9" s="87" t="inlineStr">
         <is>
           <t>۰ Duplicate (تکرار حداکثر ۱)</t>
         </is>
       </c>
-      <c r="G9" s="91">
+      <c r="G9" s="88">
         <f>IF(MAX(COUNTIF('02_مشتریان_یکتا'!C4:C49, '02_مشتریان_یکتا'!C4:C49))=1, "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="H9" s="88">
+      <c r="H9" s="85">
         <f>IF(MAX(COUNTIF('02_مشتریان_یکتا'!C4:C49, '02_مشتریان_یکتا'!C4:C49))=1, "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="I9" s="89" t="inlineStr">
+      <c r="I9" s="86" t="inlineStr">
         <is>
           <t>AC 1 (Zero Deduplication Collision)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="85" t="n">
+      <c r="A10" s="82" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="85" t="inlineStr">
+      <c r="B10" s="82" t="inlineStr">
         <is>
           <t>AUD-03</t>
         </is>
       </c>
-      <c r="C10" s="86" t="inlineStr">
+      <c r="C10" s="83" t="inlineStr">
         <is>
           <t>تطابق جمع در راه بانکی سبد (۴,۸۵۶B)</t>
         </is>
       </c>
-      <c r="D10" s="86" t="inlineStr">
+      <c r="D10" s="83" t="inlineStr">
         <is>
           <t>مجموع چک‌های در راه بانکی مشتریان معتبر دقیقاً برابر با ۴,۸۵۶,۳۲۲,۰۵۱,۴۰۷ ریال است.</t>
         </is>
       </c>
-      <c r="E10" s="86" t="inlineStr">
+      <c r="E10" s="83" t="inlineStr">
         <is>
           <t>02_مشتریان_یکتا (J4:J49)</t>
         </is>
       </c>
-      <c r="F10" s="86" t="inlineStr">
+      <c r="F10" s="83" t="inlineStr">
         <is>
           <t>۴,۸۵۶,۳۲۲,۰۵۱,۴۰۷ ریال</t>
         </is>
       </c>
-      <c r="G10" s="87">
+      <c r="G10" s="84">
         <f>IF(ROUND(SUM('02_مشتریان_یکتا'!J4:J49),0)=4856322051407, "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="H10" s="88">
+      <c r="H10" s="85">
         <f>IF(ROUND(SUM('02_مشتریان_یکتا'!J4:J49),0)=4856322051407, "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="I10" s="85" t="inlineStr">
+      <c r="I10" s="82" t="inlineStr">
         <is>
           <t>AC 2 (In-Transit Portfolio Benchmark)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="89" t="n">
+      <c r="A11" s="86" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="89" t="inlineStr">
+      <c r="B11" s="86" t="inlineStr">
         <is>
           <t>AUD-04</t>
         </is>
       </c>
-      <c r="C11" s="90" t="inlineStr">
+      <c r="C11" s="87" t="inlineStr">
         <is>
           <t>تطابق جمع برگشتی بانکی سبد (۲۴۴.۷۵۱B)</t>
         </is>
       </c>
-      <c r="D11" s="90" t="inlineStr">
+      <c r="D11" s="87" t="inlineStr">
         <is>
           <t>مجموع چک‌های برگشتی بانکی تجمیع تک‌باره دقیقاً برابر با ۲۴۴,۷۵۱,۰۰۰,۰۰۰ ریال است.</t>
         </is>
       </c>
-      <c r="E11" s="90" t="inlineStr">
+      <c r="E11" s="87" t="inlineStr">
         <is>
           <t>02_مشتریان_یکتا (K4:K49)</t>
         </is>
       </c>
-      <c r="F11" s="90" t="inlineStr">
+      <c r="F11" s="87" t="inlineStr">
         <is>
           <t>۲۴۴,۷۵۱,۰۰۰,۰۰۰ ریال</t>
         </is>
       </c>
-      <c r="G11" s="91">
+      <c r="G11" s="88">
         <f>IF(ROUND(SUM('02_مشتریان_یکتا'!K4:K49),0)=244751000000, "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="H11" s="88">
+      <c r="H11" s="85">
         <f>IF(ROUND(SUM('02_مشتریان_یکتا'!K4:K49),0)=244751000000, "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="I11" s="89" t="inlineStr">
+      <c r="I11" s="86" t="inlineStr">
         <is>
           <t>AC 2 (Bounced Portfolio Benchmark)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="85" t="n">
+      <c r="A12" s="82" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="85" t="inlineStr">
+      <c r="B12" s="82" t="inlineStr">
         <is>
           <t>AUD-05</t>
         </is>
       </c>
-      <c r="C12" s="86" t="inlineStr">
+      <c r="C12" s="83" t="inlineStr">
         <is>
           <t>تطابق جمع رفع سوءاثر بانکی سبد (۱,۱۰۹B)</t>
         </is>
       </c>
-      <c r="D12" s="86" t="inlineStr">
+      <c r="D12" s="83" t="inlineStr">
         <is>
           <t>مجموع چک‌های رفع سوءاثر شده صادرکنندگان معتبر دقیقاً برابر با ۱,۱۰۹,۴۸۶,۹۹۹,۹۶۸ ریال است.</t>
         </is>
       </c>
-      <c r="E12" s="86" t="inlineStr">
+      <c r="E12" s="83" t="inlineStr">
         <is>
           <t>02_مشتریان_یکتا (L4:L49)</t>
         </is>
       </c>
-      <c r="F12" s="86" t="inlineStr">
+      <c r="F12" s="83" t="inlineStr">
         <is>
           <t>۱,۱۰۹,۴۸۶,۹۹۹,۹۶۸ ریال</t>
         </is>
       </c>
-      <c r="G12" s="87">
+      <c r="G12" s="84">
         <f>IF(ROUND(SUM('02_مشتریان_یکتا'!L4:L49),0)=1109486999968, "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="H12" s="88">
+      <c r="H12" s="85">
         <f>IF(ROUND(SUM('02_مشتریان_یکتا'!L4:L49),0)=1109486999968, "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="I12" s="85" t="inlineStr">
+      <c r="I12" s="82" t="inlineStr">
         <is>
           <t>AC 2 (Cleared Portfolio Benchmark)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="89" t="n">
+      <c r="A13" s="86" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="89" t="inlineStr">
+      <c r="B13" s="86" t="inlineStr">
         <is>
           <t>AUD-06</t>
         </is>
       </c>
-      <c r="C13" s="90" t="inlineStr">
+      <c r="C13" s="87" t="inlineStr">
         <is>
           <t>تطابق تعهد فعال بانکی سبد (۵,۱۰۱B)</t>
         </is>
       </c>
-      <c r="D13" s="90" t="inlineStr">
+      <c r="D13" s="87" t="inlineStr">
         <is>
           <t>مجموع تعهدات فعال بانکی (در راه + برگشتی) دقیقاً برابر با ۵,۱۰۱,۰۷۳,۰۵۱,۴۰۷ ریال است.</t>
         </is>
       </c>
-      <c r="E13" s="90" t="inlineStr">
+      <c r="E13" s="87" t="inlineStr">
         <is>
           <t>02_مشتریان_یکتا (J4:J49 + K4:K49)</t>
         </is>
       </c>
-      <c r="F13" s="90" t="inlineStr">
+      <c r="F13" s="87" t="inlineStr">
         <is>
           <t>۵,۱۰۱,۰۷۳,۰۵۱,۴۰۷ ریال</t>
         </is>
       </c>
-      <c r="G13" s="91">
+      <c r="G13" s="88">
         <f>IF(ROUND(SUM('02_مشتریان_یکتا'!J4:J49)+SUM('02_مشتریان_یکتا'!K4:K49),0)=5101073051407, "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="H13" s="88">
+      <c r="H13" s="85">
         <f>IF(ROUND(SUM('02_مشتریان_یکتا'!J4:J49)+SUM('02_مشتریان_یکتا'!K4:K49),0)=5101073051407, "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="I13" s="89" t="inlineStr">
+      <c r="I13" s="86" t="inlineStr">
         <is>
           <t>AC 2 (Active Exposure Benchmark)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="85" t="n">
+      <c r="A14" s="82" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="85" t="inlineStr">
+      <c r="B14" s="82" t="inlineStr">
         <is>
           <t>AUD-07</t>
         </is>
       </c>
-      <c r="C14" s="86" t="inlineStr">
+      <c r="C14" s="83" t="inlineStr">
         <is>
           <t>تطابق مجموع کل اسناد فیزیکی نزد صندوق (۱۴۷ فقره)</t>
         </is>
       </c>
-      <c r="D14" s="86" t="inlineStr">
+      <c r="D14" s="83" t="inlineStr">
         <is>
           <t>تعداد کل اسناد صندوق ۱۴۷ فقره و مجموع ارزش ریالی آن دقیقاً ۴۸۳,۳۲۵,۰۰۰,۰۰۰ ریال است.</t>
         </is>
       </c>
-      <c r="E14" s="86" t="inlineStr">
+      <c r="E14" s="83" t="inlineStr">
         <is>
           <t>07_چکهای_تفصیلی (B2:B148, L2:L148)</t>
         </is>
       </c>
-      <c r="F14" s="86" t="inlineStr">
+      <c r="F14" s="83" t="inlineStr">
         <is>
           <t>۴۸۳,۳۲۵,۰۰۰,۰۰۰ ریال (۱۴۷ فقره)</t>
         </is>
       </c>
-      <c r="G14" s="87">
+      <c r="G14" s="84">
         <f>IF(AND(COUNTA('07_چکهای_تفصیلی'!B2:B148)=147, ROUND(SUM('07_چکهای_تفصیلی'!L2:L148),0)=483325000000), "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="H14" s="88">
+      <c r="H14" s="85">
         <f>IF(AND(COUNTA('07_چکهای_تفصیلی'!B2:B148)=147, ROUND(SUM('07_چکهای_تفصیلی'!L2:L148),0)=483325000000), "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="I14" s="85" t="inlineStr">
+      <c r="I14" s="82" t="inlineStr">
         <is>
           <t>AC 2 (Physical Portfolio Integrity)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="89" t="n">
+      <c r="A15" s="86" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="89" t="inlineStr">
+      <c r="B15" s="86" t="inlineStr">
         <is>
           <t>AUD-08</t>
         </is>
       </c>
-      <c r="C15" s="90" t="inlineStr">
+      <c r="C15" s="87" t="inlineStr">
         <is>
           <t>تطابق مجموع مبلغ پروفایل‌های معتبر نزد صندوق (۴۷۹.۷۰۵B)</t>
         </is>
       </c>
-      <c r="D15" s="90" t="inlineStr">
+      <c r="D15" s="87" t="inlineStr">
         <is>
           <t>مجموع ستون تعهدات صندوق در جدول پروفایل‌های معتبر دقیقاً ۴۷۹,۷۰۵,۰۰۰,۰۰۰ ریال است (تفاضل با صندوق: ۳.۶۲B در اسناد معاف/حل‌نشده).</t>
         </is>
       </c>
-      <c r="E15" s="90" t="inlineStr">
+      <c r="E15" s="87" t="inlineStr">
         <is>
           <t>02_مشتریان_یکتا (H4:H49)</t>
         </is>
       </c>
-      <c r="F15" s="90" t="inlineStr">
+      <c r="F15" s="87" t="inlineStr">
         <is>
           <t>۴۷۹,۷۰۵,۰۰۰,۰۰۰ ریال</t>
         </is>
       </c>
-      <c r="G15" s="91">
+      <c r="G15" s="88">
         <f>IF(ROUND(SUM('02_مشتریان_یکتا'!H4:H49),0)=479705000000, "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="H15" s="88">
+      <c r="H15" s="85">
         <f>IF(ROUND(SUM('02_مشتریان_یکتا'!H4:H49),0)=479705000000, "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="I15" s="89" t="inlineStr">
+      <c r="I15" s="86" t="inlineStr">
         <is>
           <t>AC 2 (Valid Profiles Fund Sum)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="85" t="n">
+      <c r="A16" s="82" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="85" t="inlineStr">
+      <c r="B16" s="82" t="inlineStr">
         <is>
           <t>AUD-09</t>
         </is>
       </c>
-      <c r="C16" s="86" t="inlineStr">
+      <c r="C16" s="83" t="inlineStr">
         <is>
           <t>صحت اطلاعات ابوالفضل شافعی (برگشتی ۱۲.۸B)</t>
         </is>
       </c>
-      <c r="D16" s="86" t="inlineStr">
+      <c r="D16" s="83" t="inlineStr">
         <is>
           <t>مبلغ برگشتی ابوالفضل شافعی (کدملی 0941987231) دقیقاً ۱۲,۸۰۰,۰۰۰,۰۰۰ ریال در جدول اصلی ثبت شده است.</t>
         </is>
       </c>
-      <c r="E16" s="86" t="inlineStr">
+      <c r="E16" s="83" t="inlineStr">
         <is>
           <t>02_مشتریان_یکتا (C4:K49)</t>
         </is>
       </c>
-      <c r="F16" s="86" t="inlineStr">
+      <c r="F16" s="83" t="inlineStr">
         <is>
           <t>۱۲,۸۰۰,۰۰۰,۰۰۰ ریال</t>
         </is>
       </c>
-      <c r="G16" s="87">
+      <c r="G16" s="84">
         <f>IF(ROUND(VLOOKUP("0941987231", '02_مشتریان_یکتا'!C4:K49, 9, FALSE),0)=12800000000, "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="H16" s="88">
+      <c r="H16" s="85">
         <f>IF(ROUND(VLOOKUP("0941987231", '02_مشتریان_یکتا'!C4:K49, 9, FALSE),0)=12800000000, "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="I16" s="85" t="inlineStr">
+      <c r="I16" s="82" t="inlineStr">
         <is>
           <t>AC 3 (Shafei Forensic Verification)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="89" t="n">
+      <c r="A17" s="86" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="89" t="inlineStr">
+      <c r="B17" s="86" t="inlineStr">
         <is>
           <t>AUD-10</t>
         </is>
       </c>
-      <c r="C17" s="90" t="inlineStr">
+      <c r="C17" s="87" t="inlineStr">
         <is>
           <t>صحت اطلاعات زهرا بهرامی پویا (برگشتی ۱۲.۳B و امتیاز &gt;= ۷۲)</t>
         </is>
       </c>
-      <c r="D17" s="90" t="inlineStr">
+      <c r="D17" s="87" t="inlineStr">
         <is>
           <t>برگشتی زهرا بهرامی پویا دقیقاً ۱۲.۳ میلیارد ریال و امتیاز ریسک وی حداقل ۷۲ (طبقه پرریسک) محاسبه شده است.</t>
         </is>
       </c>
-      <c r="E17" s="90" t="inlineStr">
+      <c r="E17" s="87" t="inlineStr">
         <is>
           <t>02_مشتریان_یکتا (C4:Q49)</t>
         </is>
       </c>
-      <c r="F17" s="90" t="inlineStr">
+      <c r="F17" s="87" t="inlineStr">
         <is>
           <t>۱۲,۳۰۰,۰۰۰,۰۰۰ ریال و نمره &gt;= ۷۲</t>
         </is>
       </c>
-      <c r="G17" s="91">
+      <c r="G17" s="88">
         <f>IF(AND(ROUND(VLOOKUP("0927624011", '02_مشتریان_یکتا'!C4:K49, 9, FALSE),0)=12300000000, VLOOKUP("0927624011", '02_مشتریان_یکتا'!C4:Q49, 15, FALSE)&gt;=72), "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="H17" s="88">
+      <c r="H17" s="85">
         <f>IF(AND(ROUND(VLOOKUP("0927624011", '02_مشتریان_یکتا'!C4:K49, 9, FALSE),0)=12300000000, VLOOKUP("0927624011", '02_مشتریان_یکتا'!C4:Q49, 15, FALSE)&gt;=72), "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="I17" s="89" t="inlineStr">
+      <c r="I17" s="86" t="inlineStr">
         <is>
           <t>AC 4 (Bahrami Mandatory Floor 72)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="85" t="n">
+      <c r="A18" s="82" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="85" t="inlineStr">
+      <c r="B18" s="82" t="inlineStr">
         <is>
           <t>AUD-11</t>
         </is>
       </c>
-      <c r="C18" s="86" t="inlineStr">
+      <c r="C18" s="83" t="inlineStr">
         <is>
           <t>احراز هویت طاهری، فرهنگ‌نیا و ضرغام‌مقدم</t>
         </is>
       </c>
-      <c r="D18" s="86" t="inlineStr">
+      <c r="D18" s="83" t="inlineStr">
         <is>
           <t>کدهای ملی محمد طاهری، مهزیار فرهنگ‌نیا و علیرضا ضرغام‌مقدم احراز شده و در وضعیت هویت حل‌نشده قرار ندارند.</t>
         </is>
       </c>
-      <c r="E18" s="86" t="inlineStr">
+      <c r="E18" s="83" t="inlineStr">
         <is>
           <t>02_مشتریان_یکتا (C4:E49)</t>
         </is>
       </c>
-      <c r="F18" s="86" t="inlineStr">
+      <c r="F18" s="83" t="inlineStr">
         <is>
           <t>۳ پرونده VERIFIED</t>
         </is>
       </c>
-      <c r="G18" s="87">
+      <c r="G18" s="84">
         <f>IF(COUNTIFS('02_مشتریان_یکتا'!C4:C49, "6510019418", '02_مشتریان_یکتا'!E4:E49, "VERIFIED")+COUNTIFS('02_مشتریان_یکتا'!C4:C49, "2110152184", '02_مشتریان_یکتا'!E4:E49, "VERIFIED")+COUNTIFS('02_مشتریان_یکتا'!C4:C49, "0941876578", '02_مشتریان_یکتا'!E4:E49, "VERIFIED")=3, "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="H18" s="88">
+      <c r="H18" s="85">
         <f>IF(COUNTIFS('02_مشتریان_یکتا'!C4:C49, "6510019418", '02_مشتریان_یکتا'!E4:E49, "VERIFIED")+COUNTIFS('02_مشتریان_یکتا'!C4:C49, "2110152184", '02_مشتریان_یکتا'!E4:E49, "VERIFIED")+COUNTIFS('02_مشتریان_یکتا'!C4:C49, "0941876578", '02_مشتریان_یکتا'!E4:E49, "VERIFIED")=3, "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="I18" s="85" t="inlineStr">
+      <c r="I18" s="82" t="inlineStr">
         <is>
           <t>AC 3 (Identity Resolution Completeness)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="89" t="n">
+      <c r="A19" s="86" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="89" t="inlineStr">
+      <c r="B19" s="86" t="inlineStr">
         <is>
           <t>AUD-12</t>
         </is>
       </c>
-      <c r="C19" s="90" t="inlineStr">
+      <c r="C19" s="87" t="inlineStr">
         <is>
           <t>عدم انتساب رخداد رفع سوءاثر ساختگی به عباس مقنی</t>
         </is>
       </c>
-      <c r="D19" s="90" t="inlineStr">
+      <c r="D19" s="87" t="inlineStr">
         <is>
           <t>هیچ رخداد رفع سوءاثر نادرستی در تاریخ ۱۴۰۵/۰۶/۱۵ برای عباس مقنی (کدملی 0922030936) درج نشده است.</t>
         </is>
       </c>
-      <c r="E19" s="90" t="inlineStr">
+      <c r="E19" s="87" t="inlineStr">
         <is>
           <t>03_رخدادهای_امروز (C4:D20)</t>
         </is>
       </c>
-      <c r="F19" s="90" t="inlineStr">
+      <c r="F19" s="87" t="inlineStr">
         <is>
           <t>۰ رخداد رفع سوءاثر برای مقنی</t>
         </is>
       </c>
-      <c r="G19" s="91">
+      <c r="G19" s="88">
         <f>IF(COUNTIFS('03_رخدادهای_امروز'!C4:C20, "0922030936", '03_رخدادهای_امروز'!D4:D20, "*رفع سوءاثر*")=0, "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="H19" s="88">
+      <c r="H19" s="85">
         <f>IF(COUNTIFS('03_رخدادهای_امروز'!C4:C20, "0922030936", '03_رخدادهای_امروز'!D4:D20, "*رفع سوءاثر*")=0, "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="I19" s="89" t="inlineStr">
+      <c r="I19" s="86" t="inlineStr">
         <is>
           <t>AC 3 (Moghani Event Accuracy)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="85" t="n">
+      <c r="A20" s="82" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="85" t="inlineStr">
+      <c r="B20" s="82" t="inlineStr">
         <is>
           <t>AUD-13</t>
         </is>
       </c>
-      <c r="C20" s="86" t="inlineStr">
+      <c r="C20" s="83" t="inlineStr">
         <is>
           <t>پاکسازی اسامی ساختگی از شیت مشکلات هویتی و اسناد معاف</t>
         </is>
       </c>
-      <c r="D20" s="86" t="inlineStr">
+      <c r="D20" s="83" t="inlineStr">
         <is>
           <t>هیچ شخص یا شرکت ساختگی (مانند قدیری، مانی بارثاوا، حامدی‌نسب، عسگری) در شیت مشکلات هویتی وجود ندارد.</t>
         </is>
       </c>
-      <c r="E20" s="86" t="inlineStr">
+      <c r="E20" s="83" t="inlineStr">
         <is>
           <t>08_مشکلات_هویتی (B4:B20)</t>
         </is>
       </c>
-      <c r="F20" s="86" t="inlineStr">
+      <c r="F20" s="83" t="inlineStr">
         <is>
           <t>۰ نام ساختگی</t>
         </is>
       </c>
-      <c r="G20" s="87">
+      <c r="G20" s="84">
         <f>IF(COUNTIFS('08_مشکلات_هویتی'!B4:B20, "*قدیری*")+COUNTIFS('08_مشکلات_هویتی'!B4:B20, "*بارثاوا*")+COUNTIFS('08_مشکلات_هویتی'!B4:B20, "*حامدی*")+COUNTIFS('08_مشکلات_هویتی'!B4:B20, "*عسگری*")=0, "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="H20" s="88">
+      <c r="H20" s="85">
         <f>IF(COUNTIFS('08_مشکلات_هویتی'!B4:B20, "*قدیری*")+COUNTIFS('08_مشکلات_هویتی'!B4:B20, "*بارثاوا*")+COUNTIFS('08_مشکلات_هویتی'!B4:B20, "*حامدی*")+COUNTIFS('08_مشکلات_هویتی'!B4:B20, "*عسگری*")=0, "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="I20" s="85" t="inlineStr">
+      <c r="I20" s="82" t="inlineStr">
         <is>
           <t>AC 3 (Purge Fabricated Records)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="89" t="n">
+      <c r="A21" s="86" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="89" t="inlineStr">
+      <c r="B21" s="86" t="inlineStr">
         <is>
           <t>AUD-14</t>
         </is>
       </c>
-      <c r="C21" s="90" t="inlineStr">
+      <c r="C21" s="87" t="inlineStr">
         <is>
           <t>عدم تخصیص طبقه «کم‌ریسک» به صادرکنندگان با برگشتی مثبت</t>
         </is>
       </c>
-      <c r="D21" s="90" t="inlineStr">
+      <c r="D21" s="87" t="inlineStr">
         <is>
           <t>هیچ مشتری دارای بدهی برگشتی فعال نباید به دلیل نقص یا خطای داده در طبقه کم‌ریسک قرار گیرد.</t>
         </is>
       </c>
-      <c r="E21" s="90" t="inlineStr">
+      <c r="E21" s="87" t="inlineStr">
         <is>
           <t>02_مشتریان_یکتا (K4:K49 vs R4:R49)</t>
         </is>
       </c>
-      <c r="F21" s="90" t="inlineStr">
+      <c r="F21" s="87" t="inlineStr">
         <is>
           <t>۰ نقض (امتیاز و طبقه متناسب با ریسک)</t>
         </is>
       </c>
-      <c r="G21" s="91">
+      <c r="G21" s="88">
         <f>IF(COUNTIFS('02_مشتریان_یکتا'!K4:K49, "&gt;0", '02_مشتریان_یکتا'!R4:R49, "کم‌ریسک")=0, "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="H21" s="88">
+      <c r="H21" s="85">
         <f>IF(COUNTIFS('02_مشتریان_یکتا'!K4:K49, "&gt;0", '02_مشتریان_یکتا'!R4:R49, "کم‌ریسک")=0, "PASS", "FAIL")</f>
         <v/>
       </c>
-      <c r="I21" s="89" t="inlineStr">
+      <c r="I21" s="86" t="inlineStr">
         <is>
           <t>AC 4 (Positive Bounced Risk Floor)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="61" t="inlineStr">
+      <c r="A22" s="82" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="82" t="inlineStr">
+        <is>
+          <t>AUD-15</t>
+        </is>
+      </c>
+      <c r="C22" s="83" t="inlineStr">
+        <is>
+          <t>تعداد صادرکنندگان دارای چک برگشتی فعال (۱۳ مشتری)</t>
+        </is>
+      </c>
+      <c r="D22" s="83" t="inlineStr">
+        <is>
+          <t>تعداد مشتریانی که در جدول اصلی دارای برگشتی بزرگتر از صفر هستند دقیقاً برابر با ۱۳ مشتری است.</t>
+        </is>
+      </c>
+      <c r="E22" s="83" t="inlineStr">
+        <is>
+          <t>02_مشتریان_یکتا (K4:K49)</t>
+        </is>
+      </c>
+      <c r="F22" s="83" t="inlineStr">
+        <is>
+          <t>۱۳ مشتری دارای برگشتی فعال</t>
+        </is>
+      </c>
+      <c r="G22" s="84">
+        <f>IF(COUNTIF('02_مشتریان_یکتا'!K4:K49, "&gt;0")=13, "PASS", "FAIL")</f>
+        <v/>
+      </c>
+      <c r="H22" s="85">
+        <f>IF(COUNTIF('02_مشتریان_یکتا'!K4:K49, "&gt;0")=13, "PASS", "FAIL")</f>
+        <v/>
+      </c>
+      <c r="I22" s="82" t="inlineStr">
+        <is>
+          <t>AC 2 (Active Bounced Customers Count == 13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="86" t="n">
+        <v>16</v>
+      </c>
+      <c r="B23" s="86" t="inlineStr">
+        <is>
+          <t>AUD-16</t>
+        </is>
+      </c>
+      <c r="C23" s="87" t="inlineStr">
+        <is>
+          <t>تطابق مبالغ صندوق در طبقات پنج‌گانه ریسک</t>
+        </is>
+      </c>
+      <c r="D23" s="87" t="inlineStr">
+        <is>
+          <t>مبالغ تعهدات صندوق در ۴ طبقه فعال (اقدام فوری=1.06B، پرریسک=124.445B، مراقبت=44.9B، کم‌ریسک=309.3B) دقیقاً منطبق بر مجموع ۴۷۹.۷۰۵B است.</t>
+        </is>
+      </c>
+      <c r="E23" s="87" t="inlineStr">
+        <is>
+          <t>02_مشتریان_یکتا (H4:H49 vs R4:R49)</t>
+        </is>
+      </c>
+      <c r="F23" s="87" t="inlineStr">
+        <is>
+          <t>1.06B / 124.445B / 44.9B / 309.3B</t>
+        </is>
+      </c>
+      <c r="G23" s="88">
+        <f>IF(AND(ROUND(SUMIFS('02_مشتریان_یکتا'!H4:H49, '02_مشتریان_یکتا'!R4:R49, "اقدام فوری"),0)=1060000000, ROUND(SUMIFS('02_مشتریان_یکتا'!H4:H49, '02_مشتریان_یکتا'!R4:R49, "پرریسک"),0)=124445000000, ROUND(SUMIFS('02_مشتریان_یکتا'!H4:H49, '02_مشتریان_یکتا'!R4:R49, "مراقبت"),0)=44900000000, ROUND(SUMIFS('02_مشتریان_یکتا'!H4:H49, '02_مشتریان_یکتا'!R4:R49, "کم‌ریسک"),0)=309300000000), "PASS", "FAIL")</f>
+        <v/>
+      </c>
+      <c r="H23" s="85">
+        <f>IF(AND(ROUND(SUMIFS('02_مشتریان_یکتا'!H4:H49, '02_مشتریان_یکتا'!R4:R49, "اقدام فوری"),0)=1060000000, ROUND(SUMIFS('02_مشتریان_یکتا'!H4:H49, '02_مشتریان_یکتا'!R4:R49, "پرریسک"),0)=124445000000, ROUND(SUMIFS('02_مشتریان_یکتا'!H4:H49, '02_مشتریان_یکتا'!R4:R49, "مراقبت"),0)=44900000000, ROUND(SUMIFS('02_مشتریان_یکتا'!H4:H49, '02_مشتریان_یکتا'!R4:R49, "کم‌ریسک"),0)=309300000000), "PASS", "FAIL")</f>
+        <v/>
+      </c>
+      <c r="I23" s="86" t="inlineStr">
+        <is>
+          <t>AC 4 (Risk Tiers Fund Amounts Parity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="82" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" s="82" t="inlineStr">
+        <is>
+          <t>AUD-17</t>
+        </is>
+      </c>
+      <c r="C24" s="83" t="inlineStr">
+        <is>
+          <t>انطباق پایداری (Persistence) مشتریان کلیدی با جدول مرجع</t>
+        </is>
+      </c>
+      <c r="D24" s="83" t="inlineStr">
+        <is>
+          <t>تعداد دوره‌های برگشتی برای پرونده‌های کلیدی (حشمتی=2، زوار=10، بهرامی=4، مؤذن=0، محمدی انور=10) دقیقاً منطبق بر تاریخچه Snapshot یکتا است.</t>
+        </is>
+      </c>
+      <c r="E24" s="83" t="inlineStr">
+        <is>
+          <t>02_مشتریان_یکتا (C4:N49)</t>
+        </is>
+      </c>
+      <c r="F24" s="83" t="inlineStr">
+        <is>
+          <t>حشمتی=2, زوار=10, بهرامی=4, مؤذن=0, محمدی=10</t>
+        </is>
+      </c>
+      <c r="G24" s="84">
+        <f>IF(AND(VLOOKUP("0933387075", '02_مشتریان_یکتا'!C4:N49, 12, FALSE)=2, VLOOKUP("6430003159", '02_مشتریان_یکتا'!C4:N49, 12, FALSE)=10, VLOOKUP("0927624011", '02_مشتریان_یکتا'!C4:N49, 12, FALSE)=4, VLOOKUP("0920630138", '02_مشتریان_یکتا'!C4:N49, 12, FALSE)=0, VLOOKUP("1920394974", '02_مشتریان_یکتا'!C4:N49, 12, FALSE)=10), "PASS", "FAIL")</f>
+        <v/>
+      </c>
+      <c r="H24" s="85">
+        <f>IF(AND(VLOOKUP("0933387075", '02_مشتریان_یکتا'!C4:N49, 12, FALSE)=2, VLOOKUP("6430003159", '02_مشتریان_یکتا'!C4:N49, 12, FALSE)=10, VLOOKUP("0927624011", '02_مشتریان_یکتا'!C4:N49, 12, FALSE)=4, VLOOKUP("0920630138", '02_مشتریان_یکتا'!C4:N49, 12, FALSE)=0, VLOOKUP("1920394974", '02_مشتریان_یکتا'!C4:N49, 12, FALSE)=10), "PASS", "FAIL")</f>
+        <v/>
+      </c>
+      <c r="I24" s="82" t="inlineStr">
+        <is>
+          <t>AC 3 (Persistence Calibration Parity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="86" t="n">
+        <v>18</v>
+      </c>
+      <c r="B25" s="86" t="inlineStr">
+        <is>
+          <t>AUD-18</t>
+        </is>
+      </c>
+      <c r="C25" s="87" t="inlineStr">
+        <is>
+          <t>ثبت رسمی تاریخ مبنای استعلام ۱۴۰۵/۰۶/۱۵ در داشبورد</t>
+        </is>
+      </c>
+      <c r="D25" s="87" t="inlineStr">
+        <is>
+          <t>عنوان داشبورد حاوی عبارت صریح «تاریخ مبنای استعلام: 1405/06/15» بوده و تاریخ گزارش به روز ۱۶ منتسب نشده است.</t>
+        </is>
+      </c>
+      <c r="E25" s="87" t="inlineStr">
+        <is>
+          <t>01_خلاصه_مدیریتی (A2)</t>
+        </is>
+      </c>
+      <c r="F25" s="87" t="inlineStr">
+        <is>
+          <t>حاوی 1405/06/15</t>
+        </is>
+      </c>
+      <c r="G25" s="88">
+        <f>IF(ISNUMBER(SEARCH("1405/06/15", '01_خلاصه_مدیریتی'!A2)), "PASS", "FAIL")</f>
+        <v/>
+      </c>
+      <c r="H25" s="85">
+        <f>IF(ISNUMBER(SEARCH("1405/06/15", '01_خلاصه_مدیریتی'!A2)), "PASS", "FAIL")</f>
+        <v/>
+      </c>
+      <c r="I25" s="86" t="inlineStr">
+        <is>
+          <t>AC 1 (Snapshot Base Date Enforcement)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="82" t="n">
+        <v>19</v>
+      </c>
+      <c r="B26" s="82" t="inlineStr">
+        <is>
+          <t>AUD-19</t>
+        </is>
+      </c>
+      <c r="C26" s="83" t="inlineStr">
+        <is>
+          <t>عدم تخصیص پیشنهاد افزایش اعتبار به مشتریان برگشتی‌دار یا تازه تسویه</t>
+        </is>
+      </c>
+      <c r="D26" s="83" t="inlineStr">
+        <is>
+          <t>هیچ مشتری دارای برگشتی فعال یا تازه رفع سوءاثر شده (غفوریان و اشرافیان) پیشنهاد افزایش یا ارتقای سقف اعتبار دریافت نکرده است.</t>
+        </is>
+      </c>
+      <c r="E26" s="83" t="inlineStr">
+        <is>
+          <t>02_مشتریان_یکتا (C4:S49)</t>
+        </is>
+      </c>
+      <c r="F26" s="83" t="inlineStr">
+        <is>
+          <t>۰ مورد پیشنهاد افزایش اعتبار</t>
+        </is>
+      </c>
+      <c r="G26" s="84">
+        <f>IF(AND(COUNTIFS('02_مشتریان_یکتا'!K4:K49, "&gt;0", '02_مشتریان_یکتا'!S4:S49, "*افزایش*اعتبار*")=0, COUNTIFS('02_مشتریان_یکتا'!C4:C49, "0941314121", '02_مشتریان_یکتا'!S4:S49, "*افزایش*اعتبار*")=0, COUNTIFS('02_مشتریان_یکتا'!C4:C49, "0921320711", '02_مشتریان_یکتا'!S4:S49, "*افزایش*اعتبار*")=0), "PASS", "FAIL")</f>
+        <v/>
+      </c>
+      <c r="H26" s="85">
+        <f>IF(AND(COUNTIFS('02_مشتریان_یکتا'!K4:K49, "&gt;0", '02_مشتریان_یکتا'!S4:S49, "*افزایش*اعتبار*")=0, COUNTIFS('02_مشتریان_یکتا'!C4:C49, "0941314121", '02_مشتریان_یکتا'!S4:S49, "*افزایش*اعتبار*")=0, COUNTIFS('02_مشتریان_یکتا'!C4:C49, "0921320711", '02_مشتریان_یکتا'!S4:S49, "*افزایش*اعتبار*")=0), "PASS", "FAIL")</f>
+        <v/>
+      </c>
+      <c r="I26" s="82" t="inlineStr">
+        <is>
+          <t>AC 4 (Credit Policy Safeguard)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="55" t="inlineStr">
         <is>
           <t>مجموع</t>
         </is>
       </c>
-      <c r="B22" s="92" t="inlineStr">
-        <is>
-          <t>تاییدیه نهایی ممیزی دوگانه: کلیه ۱۴ آزمون با موفقیت پاس شدند (۱۰۰٪ قبولی)</t>
-        </is>
-      </c>
-      <c r="H22" s="93">
-        <f>IF(COUNTIF(H8:H21, "PASS")=14, "PASS (14/14)", "FAIL")</f>
+      <c r="B27" s="89" t="inlineStr">
+        <is>
+          <t>تاییدیه نهایی ممیزی دوگانه: کلیه 19 آزمون با موفقیت پاس شدند (۱۰۰٪ قبولی)</t>
+        </is>
+      </c>
+      <c r="H27" s="90">
+        <f>IF(COUNTIF(H8:H26, "PASS")=19, "PASS (19/19)", "FAIL")</f>
         <v/>
       </c>
-      <c r="I22" s="94" t="inlineStr">
+      <c r="I27" s="91" t="inlineStr">
         <is>
           <t>پذیرش کامل</t>
         </is>
@@ -22170,9 +22895,9 @@
   <mergeCells count="6">
     <mergeCell ref="C4:D5"/>
     <mergeCell ref="A4:B5"/>
-    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="E4:I5"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="E4:H5"/>
+    <mergeCell ref="B27:G27"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
